--- a/Excel/23-div-25q4.xlsx
+++ b/Excel/23-div-25q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677B78DC-7C22-4442-AA31-E1B9C2D5F376}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFE7878B-AAEE-42D8-BAF1-23A6ECBA853F}"/>
   <bookViews>
-    <workbookView xWindow="408" yWindow="1548" windowWidth="14820" windowHeight="10764" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
+    <workbookView xWindow="12996" yWindow="1716" windowWidth="10068" windowHeight="10764" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
   </bookViews>
   <sheets>
     <sheet name="by paiddate" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
   <si>
     <t>name</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>RCL</t>
-  </si>
-  <si>
-    <t>SCC</t>
   </si>
   <si>
     <t>SENA</t>
@@ -699,6 +696,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1018,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCE875A-6415-4391-A62A-3B21647FF184}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -1080,7 +1081,7 @@
         <f>B2*C2</f>
         <v>26894.76</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="8">
         <f>D2*0.9</f>
         <v>24205.284</v>
       </c>
@@ -1116,7 +1117,7 @@
       <c r="D3" s="2">
         <v>9999</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="8">
         <v>8999.1</v>
       </c>
       <c r="F3" s="1">
@@ -1151,7 +1152,7 @@
       <c r="D4" s="2">
         <v>12302.7</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="8">
         <v>11072.43</v>
       </c>
       <c r="F4" s="1">
@@ -1175,7 +1176,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3">
         <v>0.12189999999999999</v>
@@ -1210,7 +1211,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
         <v>0.1212</v>
@@ -1280,7 +1281,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3">
         <v>0.17549999999999999</v>
@@ -1315,212 +1316,212 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9" s="3">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="C9" s="4">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="D9" s="2">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="E9" s="2">
-        <v>1350</v>
+        <v>2700</v>
       </c>
       <c r="F9" s="1">
-        <v>46113</v>
+        <v>46077</v>
       </c>
       <c r="G9" s="1">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H9" s="2">
-        <v>243000</v>
+        <v>388500</v>
       </c>
       <c r="I9" s="11">
-        <v>0.56000000000000005</v>
+        <v>0.69</v>
       </c>
       <c r="J9" s="2">
         <v>3000</v>
       </c>
       <c r="K9">
-        <v>1.23</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="C10" s="4">
-        <v>6000</v>
+        <v>7500</v>
       </c>
       <c r="D10" s="2">
-        <v>3000</v>
+        <v>10500</v>
       </c>
       <c r="E10" s="2">
-        <v>2700</v>
+        <v>9450</v>
       </c>
       <c r="F10" s="1">
-        <v>46077</v>
+        <v>46086</v>
       </c>
       <c r="G10" s="1">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H10" s="2">
-        <v>388500</v>
+        <v>240000</v>
       </c>
       <c r="I10" s="11">
-        <v>0.69</v>
+        <v>3.94</v>
       </c>
       <c r="J10" s="2">
-        <v>3000</v>
+        <v>17250</v>
       </c>
       <c r="K10">
-        <v>0.77</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3">
-        <v>1.4</v>
+        <v>0.43</v>
       </c>
       <c r="C11" s="4">
-        <v>7500</v>
+        <v>7000</v>
       </c>
       <c r="D11" s="2">
-        <v>10500</v>
+        <v>3010</v>
       </c>
       <c r="E11" s="2">
-        <v>9450</v>
+        <v>2709</v>
       </c>
       <c r="F11" s="1">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="G11" s="1">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="H11" s="2">
-        <v>240000</v>
+        <v>263900</v>
       </c>
       <c r="I11" s="11">
-        <v>3.94</v>
+        <v>1.03</v>
       </c>
       <c r="J11" s="2">
-        <v>17250</v>
+        <v>4690</v>
       </c>
       <c r="K11">
-        <v>7.19</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="3">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="C12" s="4">
-        <v>7000</v>
+        <v>75000</v>
       </c>
       <c r="D12" s="2">
-        <v>3010</v>
+        <v>52500</v>
       </c>
       <c r="E12" s="2">
-        <v>2709</v>
+        <v>47250</v>
       </c>
       <c r="F12" s="1">
-        <v>46083</v>
+        <v>46132</v>
       </c>
       <c r="G12" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H12" s="2">
-        <v>263900</v>
+        <v>1148400</v>
       </c>
       <c r="I12" s="11">
-        <v>1.03</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="J12" s="2">
-        <v>4690</v>
+        <v>71250</v>
       </c>
       <c r="K12">
-        <v>1.78</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="3">
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="C13" s="4">
-        <v>75000</v>
+        <v>27000</v>
       </c>
       <c r="D13" s="2">
-        <v>52500</v>
+        <v>7020</v>
       </c>
       <c r="E13" s="2">
-        <v>47250</v>
+        <v>6318</v>
       </c>
       <c r="F13" s="1">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="G13" s="1">
         <v>46149</v>
       </c>
       <c r="H13" s="2">
-        <v>1148400</v>
+        <v>201150</v>
       </c>
       <c r="I13" s="11">
-        <v>4.1100000000000003</v>
+        <v>3.14</v>
       </c>
       <c r="J13" s="2">
-        <v>71250</v>
+        <v>8370</v>
       </c>
       <c r="K13">
-        <v>6.2</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B14" s="3">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="C14" s="4">
-        <v>27000</v>
+        <v>10000</v>
       </c>
       <c r="D14" s="2">
-        <v>7020</v>
+        <v>5000</v>
       </c>
       <c r="E14" s="2">
-        <v>6318</v>
+        <v>4500</v>
       </c>
       <c r="F14" s="1">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="G14" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H14" s="2">
-        <v>201150</v>
+        <v>300000</v>
       </c>
       <c r="I14" s="11">
-        <v>3.14</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="2">
-        <v>8370</v>
+        <v>5000</v>
       </c>
       <c r="K14">
-        <v>4.16</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1528,265 +1529,265 @@
         <v>29</v>
       </c>
       <c r="B15" s="3">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="C15" s="4">
-        <v>10000</v>
+        <v>17500</v>
       </c>
       <c r="D15" s="2">
-        <v>5000</v>
+        <v>6650</v>
       </c>
       <c r="E15" s="2">
-        <v>4500</v>
+        <v>5985</v>
       </c>
       <c r="F15" s="1">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="G15" s="1">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="H15" s="2">
-        <v>300000</v>
+        <v>462000</v>
       </c>
       <c r="I15" s="11">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J15" s="2">
-        <v>5000</v>
+        <v>8400</v>
       </c>
       <c r="K15">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3">
-        <v>0.38</v>
+        <v>1.17</v>
       </c>
       <c r="C16" s="4">
-        <v>17500</v>
+        <v>4000</v>
       </c>
       <c r="D16" s="2">
-        <v>6650</v>
+        <f>B16*C16</f>
+        <v>4680</v>
       </c>
       <c r="E16" s="2">
-        <v>5985</v>
+        <f>D16*0.9</f>
+        <v>4212</v>
       </c>
       <c r="F16" s="1">
-        <v>46142</v>
+        <v>46094</v>
       </c>
       <c r="G16" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="H16" s="2">
-        <v>462000</v>
+        <v>99600</v>
       </c>
       <c r="I16" s="11">
-        <v>1.3</v>
+        <v>3.36</v>
       </c>
       <c r="J16" s="2">
-        <v>8400</v>
+        <v>6920</v>
       </c>
       <c r="K16">
-        <v>1.82</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B17" s="3">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="C17" s="4">
-        <v>4000</v>
+        <v>27000</v>
       </c>
       <c r="D17" s="2">
-        <f>B17*C17</f>
-        <v>4680</v>
+        <v>40500</v>
       </c>
       <c r="E17" s="2">
-        <f>D17*0.9</f>
-        <v>4212</v>
+        <v>36450</v>
       </c>
       <c r="F17" s="1">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="G17" s="1">
         <v>46157</v>
       </c>
       <c r="H17" s="2">
-        <v>99600</v>
+        <v>1047060</v>
       </c>
       <c r="I17" s="11">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="J17" s="2">
-        <v>6920</v>
+        <v>67500</v>
       </c>
       <c r="K17">
-        <v>6.95</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="3">
-        <v>1.5</v>
+        <v>0.35</v>
       </c>
       <c r="C18" s="4">
-        <v>27000</v>
+        <v>3600</v>
       </c>
       <c r="D18" s="2">
-        <v>40500</v>
+        <f>B18*C18</f>
+        <v>1260</v>
       </c>
       <c r="E18" s="2">
-        <v>36450</v>
+        <f>D18*0.9</f>
+        <v>1134</v>
       </c>
       <c r="F18" s="1">
-        <v>46092</v>
+        <v>45726</v>
       </c>
       <c r="G18" s="1">
         <v>46157</v>
       </c>
       <c r="H18" s="2">
-        <v>1047060</v>
+        <v>41040</v>
       </c>
       <c r="I18" s="11">
-        <v>3.48</v>
+        <v>1.97</v>
       </c>
       <c r="J18" s="2">
-        <v>67500</v>
+        <v>1260</v>
       </c>
       <c r="K18">
-        <v>6.45</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B19" s="3">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="C19" s="4">
-        <v>3600</v>
+        <v>1200</v>
       </c>
       <c r="D19" s="2">
-        <f>B19*C19</f>
-        <v>1260</v>
+        <v>576</v>
       </c>
       <c r="E19" s="2">
-        <f>D19*0.9</f>
-        <v>1134</v>
+        <v>518.4</v>
       </c>
       <c r="F19" s="1">
-        <v>45726</v>
+        <v>46093</v>
       </c>
       <c r="G19" s="1">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="H19" s="2">
-        <v>41040</v>
+        <v>44400</v>
       </c>
       <c r="I19" s="11">
-        <v>1.97</v>
+        <v>1.17</v>
       </c>
       <c r="J19" s="2">
-        <v>1260</v>
+        <v>948</v>
       </c>
       <c r="K19">
-        <v>3.07</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B20" s="3">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="C20" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D20" s="2">
         <v>1200</v>
       </c>
-      <c r="D20" s="2">
-        <v>576</v>
-      </c>
       <c r="E20" s="2">
-        <v>518.4</v>
+        <v>1080</v>
       </c>
       <c r="F20" s="1">
-        <v>46093</v>
+        <v>46141</v>
       </c>
       <c r="G20" s="1">
         <v>46164</v>
       </c>
       <c r="H20" s="2">
-        <v>44400</v>
+        <v>86800</v>
       </c>
       <c r="I20" s="11">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="J20" s="2">
-        <v>948</v>
+        <v>1800</v>
       </c>
       <c r="K20">
-        <v>2.14</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C21" s="4">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="D21" s="2">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="E21" s="2">
-        <v>1080</v>
+        <v>2250</v>
       </c>
       <c r="F21" s="1">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="G21" s="1">
         <v>46164</v>
       </c>
       <c r="H21" s="2">
-        <v>86800</v>
+        <v>234000</v>
       </c>
       <c r="I21" s="11">
-        <v>1.24</v>
+        <v>0.96</v>
       </c>
       <c r="J21" s="2">
-        <v>1800</v>
+        <v>12500</v>
       </c>
       <c r="K21">
-        <v>2.0699999999999998</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3">
-        <v>0.25</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="C22" s="4">
-        <v>10000</v>
+        <v>7200</v>
       </c>
       <c r="D22" s="2">
-        <v>2500</v>
+        <v>1260</v>
       </c>
       <c r="E22" s="2">
-        <v>2250</v>
+        <v>1134</v>
       </c>
       <c r="F22" s="1">
         <v>46147</v>
@@ -1795,250 +1796,215 @@
         <v>46164</v>
       </c>
       <c r="H22" s="2">
-        <v>234000</v>
+        <v>288000</v>
       </c>
       <c r="I22" s="11">
-        <v>0.96</v>
+        <v>0.39</v>
       </c>
       <c r="J22" s="2">
-        <v>12500</v>
+        <v>5040</v>
       </c>
       <c r="K22">
-        <v>5.34</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>0.17499999999999999</v>
+        <v>0.138295</v>
       </c>
       <c r="C23" s="4">
-        <v>7200</v>
+        <v>105000</v>
       </c>
       <c r="D23" s="2">
-        <v>1260</v>
+        <f>B23*C23</f>
+        <v>14520.975</v>
       </c>
       <c r="E23" s="2">
-        <v>1134</v>
+        <f>D23*0.9</f>
+        <v>13068.877500000001</v>
       </c>
       <c r="F23" s="1">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="G23" s="1">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="H23" s="2">
-        <v>288000</v>
+        <v>470400</v>
       </c>
       <c r="I23" s="11">
-        <v>0.39</v>
+        <v>2.78</v>
       </c>
       <c r="J23" s="2">
-        <v>5040</v>
+        <v>14521.5</v>
       </c>
       <c r="K23">
-        <v>1.75</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B24" s="3">
-        <v>0.138295</v>
+        <v>0.39</v>
       </c>
       <c r="C24" s="4">
-        <v>105000</v>
+        <v>1000</v>
       </c>
       <c r="D24" s="2">
         <f>B24*C24</f>
-        <v>14520.975</v>
+        <v>390</v>
       </c>
       <c r="E24" s="2">
         <f>D24*0.9</f>
-        <v>13068.877500000001</v>
+        <v>351</v>
       </c>
       <c r="F24" s="1">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="G24" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="H24" s="2">
-        <v>470400</v>
+        <v>26000</v>
       </c>
       <c r="I24" s="11">
-        <v>2.78</v>
+        <v>0.93</v>
       </c>
       <c r="J24" s="2">
-        <v>14521.5</v>
+        <v>630</v>
       </c>
       <c r="K24">
-        <v>3.09</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B25" s="3">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="C25" s="4">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="D25" s="2">
-        <f>B25*C25</f>
-        <v>390</v>
+        <v>720</v>
       </c>
       <c r="E25" s="2">
-        <f>D25*0.9</f>
-        <v>351</v>
+        <v>648</v>
       </c>
       <c r="F25" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="G25" s="1">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="H25" s="2">
-        <v>26000</v>
+        <v>44640</v>
       </c>
       <c r="I25" s="11">
-        <v>0.93</v>
+        <v>1.45</v>
       </c>
       <c r="J25" s="2">
-        <v>630</v>
+        <v>720</v>
       </c>
       <c r="K25">
-        <v>2.42</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="C26" s="4">
-        <v>9000</v>
-      </c>
-      <c r="D26" s="2">
-        <v>720</v>
-      </c>
       <c r="E26" s="2">
-        <v>648</v>
-      </c>
-      <c r="F26" s="1">
-        <v>46149</v>
-      </c>
-      <c r="G26" s="1">
-        <v>46170</v>
-      </c>
-      <c r="H26" s="2">
-        <v>44640</v>
-      </c>
-      <c r="I26" s="11">
-        <v>1.45</v>
-      </c>
-      <c r="J26" s="2">
-        <v>720</v>
-      </c>
-      <c r="K26">
-        <v>1.61</v>
+        <f>SUM(E2:E25)</f>
+        <v>209996.49149999997</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0.22412299999999999</v>
+      </c>
+      <c r="C27" s="4">
+        <v>30000</v>
+      </c>
+      <c r="D27" s="2">
+        <f>B27*C27</f>
+        <v>6723.69</v>
+      </c>
       <c r="E27" s="2">
-        <f>SUM(E2:E26)</f>
-        <v>211346.49149999997</v>
+        <f>D27*0.9</f>
+        <v>6051.3209999999999</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46066</v>
+      </c>
+      <c r="G27" s="1">
+        <v>46085</v>
+      </c>
+      <c r="H27" s="2">
+        <v>1212000</v>
+      </c>
+      <c r="I27" s="11">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>61908</v>
+      </c>
+      <c r="K27">
+        <v>5.1100000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="3">
-        <v>0.22412299999999999</v>
-      </c>
-      <c r="C28" s="4">
-        <v>30000</v>
-      </c>
-      <c r="D28" s="2">
-        <f>B28*C28</f>
-        <v>6723.69</v>
-      </c>
       <c r="E28" s="2">
-        <f>D28*0.9</f>
-        <v>6051.3209999999999</v>
-      </c>
-      <c r="F28" s="1">
-        <v>46066</v>
-      </c>
-      <c r="G28" s="1">
-        <v>46085</v>
-      </c>
-      <c r="H28" s="2">
-        <v>1212000</v>
-      </c>
-      <c r="I28" s="11">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2">
-        <v>61908</v>
-      </c>
-      <c r="K28">
-        <v>5.1100000000000003</v>
+        <f>E2+E27</f>
+        <v>30256.605</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0.27939999999999998</v>
+      </c>
+      <c r="C29" s="4">
+        <v>24000</v>
+      </c>
+      <c r="D29" s="2">
+        <f>B29*C29</f>
+        <v>6705.5999999999995</v>
+      </c>
       <c r="E29" s="2">
-        <f>E2+E28</f>
-        <v>30256.605</v>
-      </c>
+        <f>D29</f>
+        <v>6705.5999999999995</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46092</v>
+      </c>
+      <c r="G29" s="1">
+        <v>46108</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29"/>
+      <c r="J29"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="3">
-        <v>0.27939999999999998</v>
-      </c>
-      <c r="C30" s="4">
-        <v>24000</v>
-      </c>
-      <c r="D30" s="2">
-        <f>B30*C30</f>
-        <v>6705.5999999999995</v>
-      </c>
       <c r="E30" s="2">
-        <f>D30</f>
-        <v>6705.5999999999995</v>
-      </c>
-      <c r="F30" s="1">
-        <v>46092</v>
-      </c>
-      <c r="G30" s="1">
-        <v>46108</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30"/>
-      <c r="J30"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E31" s="2">
-        <f>E7+E30</f>
+        <f>E7+E29</f>
         <v>20535.899999999998</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition ref="G2:G26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition ref="G2:G25"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2046,7 +2012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867434CE-2F54-4206-8AAB-2864B8ABE9CF}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -2238,7 +2204,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3">
         <v>0.12189999999999999</v>
@@ -2308,7 +2274,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3">
         <v>0.1212</v>
@@ -2343,7 +2309,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>0.17549999999999999</v>
@@ -2555,7 +2521,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="3">
         <v>1.17</v>
@@ -2592,229 +2558,229 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B16" s="3">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="C16" s="4">
-        <v>600</v>
+        <v>75000</v>
       </c>
       <c r="D16" s="2">
-        <v>1500</v>
+        <v>52500</v>
       </c>
       <c r="E16" s="2">
-        <v>1350</v>
+        <v>47250</v>
       </c>
       <c r="F16" s="1">
-        <v>46113</v>
+        <v>46132</v>
       </c>
       <c r="G16" s="1">
-        <v>46133</v>
+        <v>46149</v>
       </c>
       <c r="H16" s="2">
-        <v>243000</v>
+        <v>1148400</v>
       </c>
       <c r="I16" s="11">
-        <v>0.56000000000000005</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="J16" s="2">
-        <v>3000</v>
+        <v>71250</v>
       </c>
       <c r="K16">
-        <v>1.23</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C17" s="4">
-        <v>75000</v>
+        <v>10000</v>
       </c>
       <c r="D17" s="2">
-        <v>52500</v>
+        <v>5000</v>
       </c>
       <c r="E17" s="2">
-        <v>47250</v>
+        <v>4500</v>
       </c>
       <c r="F17" s="1">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="G17" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H17" s="2">
-        <v>1148400</v>
+        <v>300000</v>
       </c>
       <c r="I17" s="11">
-        <v>4.1100000000000003</v>
+        <v>1.5</v>
       </c>
       <c r="J17" s="2">
-        <v>71250</v>
+        <v>5000</v>
       </c>
       <c r="K17">
-        <v>6.2</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B18" s="3">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="C18" s="4">
-        <v>10000</v>
+        <v>27000</v>
       </c>
       <c r="D18" s="2">
-        <v>5000</v>
+        <v>7020</v>
       </c>
       <c r="E18" s="2">
-        <v>4500</v>
+        <v>6318</v>
       </c>
       <c r="F18" s="1">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="G18" s="1">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="H18" s="2">
-        <v>300000</v>
+        <v>201150</v>
       </c>
       <c r="I18" s="11">
-        <v>1.5</v>
+        <v>3.14</v>
       </c>
       <c r="J18" s="2">
-        <v>5000</v>
+        <v>8370</v>
       </c>
       <c r="K18">
-        <v>1.67</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B19" s="3">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="C19" s="4">
-        <v>27000</v>
+        <v>4000</v>
       </c>
       <c r="D19" s="2">
-        <v>7020</v>
+        <v>1200</v>
       </c>
       <c r="E19" s="2">
-        <v>6318</v>
+        <v>1080</v>
       </c>
       <c r="F19" s="1">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="G19" s="1">
-        <v>46149</v>
+        <v>46164</v>
       </c>
       <c r="H19" s="2">
-        <v>201150</v>
+        <v>86800</v>
       </c>
       <c r="I19" s="11">
-        <v>3.14</v>
+        <v>1.24</v>
       </c>
       <c r="J19" s="2">
-        <v>8370</v>
+        <v>1800</v>
       </c>
       <c r="K19">
-        <v>4.16</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B20" s="3">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C20" s="4">
-        <v>4000</v>
+        <v>17500</v>
       </c>
       <c r="D20" s="2">
-        <v>1200</v>
+        <v>6650</v>
       </c>
       <c r="E20" s="2">
-        <v>1080</v>
+        <v>5985</v>
       </c>
       <c r="F20" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="G20" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="H20" s="2">
-        <v>86800</v>
+        <v>462000</v>
       </c>
       <c r="I20" s="11">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="J20" s="2">
-        <v>1800</v>
+        <v>8400</v>
       </c>
       <c r="K20">
-        <v>2.0699999999999998</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B21" s="3">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="C21" s="4">
-        <v>17500</v>
+        <v>10000</v>
       </c>
       <c r="D21" s="2">
-        <v>6650</v>
+        <v>2500</v>
       </c>
       <c r="E21" s="2">
-        <v>5985</v>
+        <v>2250</v>
       </c>
       <c r="F21" s="1">
-        <v>46142</v>
+        <v>46147</v>
       </c>
       <c r="G21" s="1">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="H21" s="2">
-        <v>462000</v>
+        <v>234000</v>
       </c>
       <c r="I21" s="11">
-        <v>1.3</v>
+        <v>0.96</v>
       </c>
       <c r="J21" s="2">
-        <v>8400</v>
+        <v>12500</v>
       </c>
       <c r="K21">
-        <v>1.82</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3">
-        <v>0.25</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="C22" s="4">
-        <v>10000</v>
+        <v>7200</v>
       </c>
       <c r="D22" s="2">
-        <v>2500</v>
+        <v>1260</v>
       </c>
       <c r="E22" s="2">
-        <v>2250</v>
+        <v>1134</v>
       </c>
       <c r="F22" s="1">
         <v>46147</v>
@@ -2823,250 +2789,215 @@
         <v>46164</v>
       </c>
       <c r="H22" s="2">
-        <v>234000</v>
+        <v>288000</v>
       </c>
       <c r="I22" s="11">
-        <v>0.96</v>
+        <v>0.39</v>
       </c>
       <c r="J22" s="2">
-        <v>12500</v>
+        <v>5040</v>
       </c>
       <c r="K22">
-        <v>5.34</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>0.17499999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="C23" s="4">
-        <v>7200</v>
+        <v>1000</v>
       </c>
       <c r="D23" s="2">
-        <v>1260</v>
+        <f>B23*C23</f>
+        <v>390</v>
       </c>
       <c r="E23" s="2">
-        <v>1134</v>
+        <f>D23*0.9</f>
+        <v>351</v>
       </c>
       <c r="F23" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="G23" s="1">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="H23" s="2">
-        <v>288000</v>
+        <v>26000</v>
       </c>
       <c r="I23" s="11">
-        <v>0.39</v>
+        <v>0.93</v>
       </c>
       <c r="J23" s="2">
-        <v>5040</v>
+        <v>630</v>
       </c>
       <c r="K23">
-        <v>1.75</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B24" s="3">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="C24" s="4">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="D24" s="2">
-        <f>B24*C24</f>
-        <v>390</v>
+        <v>720</v>
       </c>
       <c r="E24" s="2">
-        <f>D24*0.9</f>
-        <v>351</v>
+        <v>648</v>
       </c>
       <c r="F24" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="G24" s="1">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="H24" s="2">
-        <v>26000</v>
+        <v>44640</v>
       </c>
       <c r="I24" s="11">
-        <v>0.93</v>
+        <v>1.45</v>
       </c>
       <c r="J24" s="2">
-        <v>630</v>
+        <v>720</v>
       </c>
       <c r="K24">
-        <v>2.42</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B25" s="3">
-        <v>0.08</v>
+        <v>0.138295</v>
       </c>
       <c r="C25" s="4">
-        <v>9000</v>
+        <v>105000</v>
       </c>
       <c r="D25" s="2">
-        <v>720</v>
+        <f>B25*C25</f>
+        <v>14520.975</v>
       </c>
       <c r="E25" s="2">
-        <v>648</v>
+        <f>D25*0.9</f>
+        <v>13068.877500000001</v>
       </c>
       <c r="F25" s="1">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="G25" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="H25" s="2">
-        <v>44640</v>
+        <v>470400</v>
       </c>
       <c r="I25" s="11">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
       <c r="J25" s="2">
-        <v>720</v>
+        <v>14521.5</v>
       </c>
       <c r="K25">
-        <v>1.61</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="3">
-        <v>0.138295</v>
-      </c>
-      <c r="C26" s="4">
-        <v>105000</v>
-      </c>
-      <c r="D26" s="2">
-        <f>B26*C26</f>
-        <v>14520.975</v>
-      </c>
       <c r="E26" s="2">
-        <f>D26*0.9</f>
-        <v>13068.877500000001</v>
-      </c>
-      <c r="F26" s="1">
-        <v>46155</v>
-      </c>
-      <c r="G26" s="1">
-        <v>46167</v>
-      </c>
-      <c r="H26" s="2">
-        <v>470400</v>
-      </c>
-      <c r="I26" s="11">
-        <v>2.78</v>
-      </c>
-      <c r="J26" s="2">
-        <v>14521.5</v>
-      </c>
-      <c r="K26">
-        <v>3.09</v>
+        <f>SUM(E2:E25)</f>
+        <v>209996.4915</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0.22412299999999999</v>
+      </c>
+      <c r="C27" s="4">
+        <v>30000</v>
+      </c>
+      <c r="D27" s="2">
+        <f>B27*C27</f>
+        <v>6723.69</v>
+      </c>
       <c r="E27" s="2">
-        <f>SUM(E2:E26)</f>
-        <v>211346.4915</v>
+        <f>D27*0.9</f>
+        <v>6051.3209999999999</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46066</v>
+      </c>
+      <c r="G27" s="1">
+        <v>46085</v>
+      </c>
+      <c r="H27" s="2">
+        <v>1212000</v>
+      </c>
+      <c r="I27" s="11">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>61908</v>
+      </c>
+      <c r="K27">
+        <v>5.1100000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="3">
-        <v>0.22412299999999999</v>
-      </c>
-      <c r="C28" s="4">
-        <v>30000</v>
-      </c>
-      <c r="D28" s="2">
-        <f>B28*C28</f>
-        <v>6723.69</v>
-      </c>
       <c r="E28" s="2">
-        <f>D28*0.9</f>
-        <v>6051.3209999999999</v>
-      </c>
-      <c r="F28" s="1">
-        <v>46066</v>
-      </c>
-      <c r="G28" s="1">
-        <v>46085</v>
-      </c>
-      <c r="H28" s="2">
-        <v>1212000</v>
-      </c>
-      <c r="I28" s="11">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2">
-        <v>61908</v>
-      </c>
-      <c r="K28">
-        <v>5.1100000000000003</v>
+        <f>E2+E27</f>
+        <v>30256.605</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0.27939999999999998</v>
+      </c>
+      <c r="C29" s="4">
+        <v>24000</v>
+      </c>
+      <c r="D29" s="2">
+        <f>B29*C29</f>
+        <v>6705.5999999999995</v>
+      </c>
       <c r="E29" s="2">
-        <f>E2+E28</f>
-        <v>30256.605</v>
-      </c>
+        <f>D29</f>
+        <v>6705.5999999999995</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46092</v>
+      </c>
+      <c r="G29" s="1">
+        <v>46108</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29"/>
+      <c r="J29"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="3">
-        <v>0.27939999999999998</v>
-      </c>
-      <c r="C30" s="4">
-        <v>24000</v>
-      </c>
-      <c r="D30" s="2">
-        <f>B30*C30</f>
-        <v>6705.5999999999995</v>
-      </c>
       <c r="E30" s="2">
-        <f>D30</f>
-        <v>6705.5999999999995</v>
-      </c>
-      <c r="F30" s="1">
-        <v>46092</v>
-      </c>
-      <c r="G30" s="1">
-        <v>46108</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30"/>
-      <c r="J30"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E31" s="2">
-        <f>E11+E30</f>
+        <f>E11+E29</f>
         <v>7839.5999999999995</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition ref="F2:F26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition ref="F2:F25"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/23-div-25q4.xlsx
+++ b/Excel/23-div-25q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFE7878B-AAEE-42D8-BAF1-23A6ECBA853F}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC8F52E0-1E92-48CE-99E5-2C6B054ABC00}"/>
   <bookViews>
-    <workbookView xWindow="12996" yWindow="1716" windowWidth="10068" windowHeight="10764" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
+    <workbookView xWindow="11484" yWindow="1476" windowWidth="11556" windowHeight="10764" activeTab="1" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
   </bookViews>
   <sheets>
     <sheet name="by paiddate" sheetId="1" r:id="rId1"/>
@@ -1185,10 +1185,12 @@
         <v>20000</v>
       </c>
       <c r="D5" s="2">
-        <v>2280</v>
-      </c>
-      <c r="E5" s="2">
-        <v>2052</v>
+        <f>B5*C5</f>
+        <v>2438</v>
+      </c>
+      <c r="E5" s="8">
+        <f>D5*0.9</f>
+        <v>2194.2000000000003</v>
       </c>
       <c r="F5" s="1">
         <v>46080</v>
@@ -1920,7 +1922,7 @@
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E26" s="2">
         <f>SUM(E2:E25)</f>
-        <v>209996.49149999997</v>
+        <v>210138.69149999999</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -2213,10 +2215,12 @@
         <v>20000</v>
       </c>
       <c r="D6" s="2">
-        <v>2280</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2052</v>
+        <f>B6*C6</f>
+        <v>2438</v>
+      </c>
+      <c r="E6" s="8">
+        <f>D6*0.9</f>
+        <v>2194.2000000000003</v>
       </c>
       <c r="F6" s="1">
         <v>46080</v>
@@ -2913,7 +2917,7 @@
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E26" s="2">
         <f>SUM(E2:E25)</f>
-        <v>209996.4915</v>
+        <v>210138.69150000002</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">

--- a/Excel/23-div-25q4.xlsx
+++ b/Excel/23-div-25q4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC8F52E0-1E92-48CE-99E5-2C6B054ABC00}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0063A55C-30B0-426C-B81F-226F37731705}"/>
   <bookViews>
-    <workbookView xWindow="11484" yWindow="1476" windowWidth="11556" windowHeight="10764" activeTab="1" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
+    <workbookView xWindow="4584" yWindow="1284" windowWidth="17808" windowHeight="10152" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
   </bookViews>
   <sheets>
     <sheet name="by paiddate" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="35">
   <si>
     <t>name</t>
   </si>
@@ -146,29 +146,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.000000"/>
+    <numFmt numFmtId="187" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="188" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="189" formatCode="0.000000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Aptos Display"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -176,7 +176,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -184,7 +184,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -192,35 +192,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -228,7 +228,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -236,14 +236,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -251,14 +251,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -266,7 +266,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -274,14 +274,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -629,15 +629,15 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -696,10 +696,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1019,20 +1015,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCE875A-6415-4391-A62A-3B21647FF184}">
-  <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="4"/>
-    <col min="4" max="4" width="10.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="11"/>
-    <col min="10" max="10" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.8984375" style="4"/>
+    <col min="4" max="4" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.8984375" style="11"/>
+    <col min="10" max="10" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1104,7 +1101,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1139,7 +1136,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1174,7 +1171,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1211,7 +1208,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1224,7 +1221,7 @@
       <c r="D6" s="2">
         <v>2424</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="8">
         <v>2181.6</v>
       </c>
       <c r="F6" s="1">
@@ -1246,550 +1243,556 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="3">
+        <v>7.4800000000000005E-2</v>
+      </c>
+      <c r="C7" s="4">
+        <v>20000</v>
+      </c>
+      <c r="D7" s="2">
+        <f>B7*C7</f>
+        <v>1496</v>
+      </c>
+      <c r="E7" s="8">
+        <f>D7</f>
+        <v>1496</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G7" s="1">
+        <v>46101</v>
+      </c>
+      <c r="H7" s="2">
+        <v>246000</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="J7" s="2">
+        <v>13548</v>
+      </c>
+      <c r="K7">
+        <v>5.51</v>
+      </c>
+      <c r="L7" s="2">
+        <f>SUM(E2:E7)</f>
+        <v>50148.613999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B8" s="3">
         <v>0.27939999999999998</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C8" s="4">
         <v>55000</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D8" s="2">
         <v>15367</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E8" s="2">
         <v>13830.3</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F8" s="1">
         <v>46092</v>
-      </c>
-      <c r="G7" s="1">
-        <v>46108</v>
-      </c>
-      <c r="H7" s="2">
-        <v>990000</v>
-      </c>
-      <c r="I7" s="11">
-        <v>1.4</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45380.5</v>
-      </c>
-      <c r="K7">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.17549999999999999</v>
-      </c>
-      <c r="C8" s="4">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="2">
-        <v>8775</v>
-      </c>
-      <c r="E8" s="2">
-        <v>7897.5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46086</v>
       </c>
       <c r="G8" s="1">
         <v>46108</v>
       </c>
       <c r="H8" s="2">
+        <v>990000</v>
+      </c>
+      <c r="I8" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="J8" s="2">
+        <v>45380.5</v>
+      </c>
+      <c r="K8">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.17549999999999999</v>
+      </c>
+      <c r="C9" s="4">
+        <v>50000</v>
+      </c>
+      <c r="D9" s="2">
+        <v>8775</v>
+      </c>
+      <c r="E9" s="2">
+        <v>7897.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G9" s="1">
+        <v>46108</v>
+      </c>
+      <c r="H9" s="2">
         <v>435000</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I9" s="11">
         <v>1.82</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J9" s="2">
         <v>28650</v>
       </c>
-      <c r="K8">
+      <c r="K9">
         <v>6.59</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B10" s="3">
         <v>0.5</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C10" s="4">
         <v>6000</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D10" s="2">
         <v>3000</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E10" s="2">
         <v>2700</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F10" s="1">
         <v>46077</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G10" s="1">
         <v>46136</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H10" s="2">
         <v>388500</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I10" s="11">
         <v>0.69</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J10" s="2">
         <v>3000</v>
       </c>
-      <c r="K9">
+      <c r="K10">
         <v>0.77</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B11" s="3">
         <v>1.4</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C11" s="4">
         <v>7500</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D11" s="2">
         <v>10500</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E11" s="2">
         <v>9450</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>46086</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>46140</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H11" s="2">
         <v>240000</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I11" s="11">
         <v>3.94</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J11" s="2">
         <v>17250</v>
       </c>
-      <c r="K10">
+      <c r="K11">
         <v>7.19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B12" s="3">
         <v>0.43</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C12" s="4">
         <v>7000</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="2">
         <v>3010</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E12" s="2">
         <v>2709</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F12" s="1">
         <v>46083</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" s="1">
         <v>46148</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H12" s="2">
         <v>263900</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I12" s="11">
         <v>1.03</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J12" s="2">
         <v>4690</v>
       </c>
-      <c r="K11">
+      <c r="K12">
         <v>1.78</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B13" s="3">
         <v>0.7</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C13" s="4">
         <v>75000</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D13" s="2">
         <v>52500</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E13" s="2">
         <v>47250</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F13" s="1">
         <v>46132</v>
-      </c>
-      <c r="G12" s="1">
-        <v>46149</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1148400</v>
-      </c>
-      <c r="I12" s="11">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="J12" s="2">
-        <v>71250</v>
-      </c>
-      <c r="K12">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0.26</v>
-      </c>
-      <c r="C13" s="4">
-        <v>27000</v>
-      </c>
-      <c r="D13" s="2">
-        <v>7020</v>
-      </c>
-      <c r="E13" s="2">
-        <v>6318</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46135</v>
       </c>
       <c r="G13" s="1">
         <v>46149</v>
       </c>
       <c r="H13" s="2">
+        <v>1148400</v>
+      </c>
+      <c r="I13" s="11">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="J13" s="2">
+        <v>71250</v>
+      </c>
+      <c r="K13">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="C14" s="4">
+        <v>27000</v>
+      </c>
+      <c r="D14" s="2">
+        <v>7020</v>
+      </c>
+      <c r="E14" s="2">
+        <v>6318</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46135</v>
+      </c>
+      <c r="G14" s="1">
+        <v>46149</v>
+      </c>
+      <c r="H14" s="2">
         <v>201150</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I14" s="11">
         <v>3.14</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J14" s="2">
         <v>8370</v>
       </c>
-      <c r="K13">
+      <c r="K14">
         <v>4.16</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B15" s="3">
         <v>0.5</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C15" s="4">
         <v>10000</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D15" s="2">
         <v>5000</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E15" s="2">
         <v>4500</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F15" s="1">
         <v>46133</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15" s="1">
         <v>46150</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H15" s="2">
         <v>300000</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I15" s="11">
         <v>1.5</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J15" s="2">
         <v>5000</v>
       </c>
-      <c r="K14">
+      <c r="K15">
         <v>1.67</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B16" s="3">
         <v>0.38</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C16" s="4">
         <v>17500</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D16" s="2">
         <v>6650</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E16" s="2">
         <v>5985</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F16" s="1">
         <v>46142</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G16" s="1">
         <v>46154</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H16" s="2">
         <v>462000</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I16" s="11">
         <v>1.3</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J16" s="2">
         <v>8400</v>
       </c>
-      <c r="K15">
+      <c r="K16">
         <v>1.82</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B17" s="3">
         <v>1.17</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C17" s="4">
         <v>4000</v>
       </c>
-      <c r="D16" s="2">
-        <f>B16*C16</f>
+      <c r="D17" s="2">
+        <f>B17*C17</f>
         <v>4680</v>
       </c>
-      <c r="E16" s="2">
-        <f>D16*0.9</f>
+      <c r="E17" s="2">
+        <f>D17*0.9</f>
         <v>4212</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F17" s="1">
         <v>46094</v>
-      </c>
-      <c r="G16" s="1">
-        <v>46157</v>
-      </c>
-      <c r="H16" s="2">
-        <v>99600</v>
-      </c>
-      <c r="I16" s="11">
-        <v>3.36</v>
-      </c>
-      <c r="J16" s="2">
-        <v>6920</v>
-      </c>
-      <c r="K16">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="C17" s="4">
-        <v>27000</v>
-      </c>
-      <c r="D17" s="2">
-        <v>40500</v>
-      </c>
-      <c r="E17" s="2">
-        <v>36450</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46092</v>
       </c>
       <c r="G17" s="1">
         <v>46157</v>
       </c>
       <c r="H17" s="2">
-        <v>1047060</v>
+        <v>99600</v>
       </c>
       <c r="I17" s="11">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="J17" s="2">
-        <v>67500</v>
+        <v>6920</v>
       </c>
       <c r="K17">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>0.35</v>
+        <v>1.5</v>
       </c>
       <c r="C18" s="4">
-        <v>3600</v>
+        <v>27000</v>
       </c>
       <c r="D18" s="2">
-        <f>B18*C18</f>
-        <v>1260</v>
+        <v>40500</v>
       </c>
       <c r="E18" s="2">
-        <f>D18*0.9</f>
-        <v>1134</v>
+        <v>36450</v>
       </c>
       <c r="F18" s="1">
-        <v>45726</v>
+        <v>46092</v>
       </c>
       <c r="G18" s="1">
         <v>46157</v>
       </c>
       <c r="H18" s="2">
+        <v>1047060</v>
+      </c>
+      <c r="I18" s="11">
+        <v>3.48</v>
+      </c>
+      <c r="J18" s="2">
+        <v>67500</v>
+      </c>
+      <c r="K18">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="C19" s="4">
+        <v>3600</v>
+      </c>
+      <c r="D19" s="2">
+        <f>B19*C19</f>
+        <v>1260</v>
+      </c>
+      <c r="E19" s="2">
+        <f>D19*0.9</f>
+        <v>1134</v>
+      </c>
+      <c r="F19" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G19" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H19" s="2">
         <v>41040</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I19" s="11">
         <v>1.97</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J19" s="2">
         <v>1260</v>
       </c>
-      <c r="K18">
+      <c r="K19">
         <v>3.07</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B20" s="3">
         <v>0.48</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C20" s="4">
         <v>1200</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D20" s="2">
         <v>576</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E20" s="2">
         <v>518.4</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F20" s="1">
         <v>46093</v>
-      </c>
-      <c r="G19" s="1">
-        <v>46164</v>
-      </c>
-      <c r="H19" s="2">
-        <v>44400</v>
-      </c>
-      <c r="I19" s="11">
-        <v>1.17</v>
-      </c>
-      <c r="J19" s="2">
-        <v>948</v>
-      </c>
-      <c r="K19">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="C20" s="4">
-        <v>4000</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1200</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1080</v>
-      </c>
-      <c r="F20" s="1">
-        <v>46141</v>
       </c>
       <c r="G20" s="1">
         <v>46164</v>
       </c>
       <c r="H20" s="2">
-        <v>86800</v>
+        <v>44400</v>
       </c>
       <c r="I20" s="11">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="J20" s="2">
-        <v>1800</v>
+        <v>948</v>
       </c>
       <c r="K20">
-        <v>2.0699999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="3">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="C21" s="4">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="D21" s="2">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="E21" s="2">
-        <v>2250</v>
+        <v>1080</v>
       </c>
       <c r="F21" s="1">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="G21" s="1">
         <v>46164</v>
       </c>
       <c r="H21" s="2">
-        <v>234000</v>
+        <v>86800</v>
       </c>
       <c r="I21" s="11">
-        <v>0.96</v>
+        <v>1.24</v>
       </c>
       <c r="J21" s="2">
-        <v>12500</v>
+        <v>1800</v>
       </c>
       <c r="K21">
-        <v>5.34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>2.0699999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B22" s="3">
-        <v>0.17499999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="C22" s="4">
-        <v>7200</v>
+        <v>10000</v>
       </c>
       <c r="D22" s="2">
-        <v>1260</v>
+        <v>2500</v>
       </c>
       <c r="E22" s="2">
-        <v>1134</v>
+        <v>2250</v>
       </c>
       <c r="F22" s="1">
         <v>46147</v>
@@ -1798,215 +1801,254 @@
         <v>46164</v>
       </c>
       <c r="H22" s="2">
+        <v>234000</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="J22" s="2">
+        <v>12500</v>
+      </c>
+      <c r="K22">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C23" s="4">
+        <v>7200</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1260</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1134</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G23" s="1">
+        <v>46164</v>
+      </c>
+      <c r="H23" s="2">
         <v>288000</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I23" s="11">
         <v>0.39</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J23" s="2">
         <v>5040</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>1.75</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B24" s="3">
         <v>0.138295</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C24" s="4">
         <v>105000</v>
-      </c>
-      <c r="D23" s="2">
-        <f>B23*C23</f>
-        <v>14520.975</v>
-      </c>
-      <c r="E23" s="2">
-        <f>D23*0.9</f>
-        <v>13068.877500000001</v>
-      </c>
-      <c r="F23" s="1">
-        <v>46155</v>
-      </c>
-      <c r="G23" s="1">
-        <v>46167</v>
-      </c>
-      <c r="H23" s="2">
-        <v>470400</v>
-      </c>
-      <c r="I23" s="11">
-        <v>2.78</v>
-      </c>
-      <c r="J23" s="2">
-        <v>14521.5</v>
-      </c>
-      <c r="K23">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="3">
-        <v>0.39</v>
-      </c>
-      <c r="C24" s="4">
-        <v>1000</v>
       </c>
       <c r="D24" s="2">
         <f>B24*C24</f>
-        <v>390</v>
+        <v>14520.975</v>
       </c>
       <c r="E24" s="2">
         <f>D24*0.9</f>
+        <v>13068.877500000001</v>
+      </c>
+      <c r="F24" s="1">
+        <v>46155</v>
+      </c>
+      <c r="G24" s="1">
+        <v>46167</v>
+      </c>
+      <c r="H24" s="2">
+        <v>470400</v>
+      </c>
+      <c r="I24" s="11">
+        <v>2.78</v>
+      </c>
+      <c r="J24" s="2">
+        <v>14521.5</v>
+      </c>
+      <c r="K24">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="C25" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D25" s="2">
+        <f>B25*C25</f>
+        <v>390</v>
+      </c>
+      <c r="E25" s="2">
+        <f>D25*0.9</f>
         <v>351</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F25" s="1">
         <v>46148</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G25" s="1">
         <v>46168</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H25" s="2">
         <v>26000</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I25" s="11">
         <v>0.93</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J25" s="2">
         <v>630</v>
       </c>
-      <c r="K24">
+      <c r="K25">
         <v>2.42</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B26" s="3">
         <v>0.08</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C26" s="4">
         <v>9000</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D26" s="2">
         <v>720</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E26" s="2">
         <v>648</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F26" s="1">
         <v>46149</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G26" s="1">
         <v>46170</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H26" s="2">
         <v>44640</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I26" s="11">
         <v>1.45</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J26" s="2">
         <v>720</v>
       </c>
-      <c r="K25">
+      <c r="K26">
         <v>1.61</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E26" s="2">
-        <f>SUM(E2:E25)</f>
-        <v>210138.69149999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E27" s="2">
+        <f>SUM(E2:E26)</f>
+        <v>211634.69149999999</v>
+      </c>
+      <c r="L27" s="2">
+        <f>E27-L7</f>
+        <v>161486.07749999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B28" s="3">
         <v>0.22412299999999999</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C28" s="4">
         <v>30000</v>
       </c>
-      <c r="D27" s="2">
-        <f>B27*C27</f>
+      <c r="D28" s="2">
+        <f>B28*C28</f>
         <v>6723.69</v>
       </c>
-      <c r="E27" s="2">
-        <f>D27*0.9</f>
+      <c r="E28" s="2">
+        <f>D28*0.9</f>
         <v>6051.3209999999999</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F28" s="1">
         <v>46066</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G28" s="1">
         <v>46085</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H28" s="2">
         <v>1212000</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I28" s="11">
         <v>2</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J28" s="2">
         <v>61908</v>
       </c>
-      <c r="K27">
+      <c r="K28">
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E28" s="2">
-        <f>E2+E27</f>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E29" s="2">
+        <f>E2+E28</f>
         <v>30256.605</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>0.27939999999999998</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C30" s="4">
         <v>24000</v>
       </c>
-      <c r="D29" s="2">
-        <f>B29*C29</f>
+      <c r="D30" s="2">
+        <f>B30*C30</f>
         <v>6705.5999999999995</v>
       </c>
-      <c r="E29" s="2">
-        <f>D29</f>
+      <c r="E30" s="2">
+        <f>D30</f>
         <v>6705.5999999999995</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F30" s="1">
         <v>46092</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G30" s="1">
         <v>46108</v>
       </c>
-      <c r="H29">
+      <c r="H30">
         <v>1</v>
       </c>
-      <c r="I29"/>
-      <c r="J29"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E30" s="2">
-        <f>E7+E29</f>
+      <c r="I30"/>
+      <c r="J30"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E31" s="2">
+        <f>E8+E30</f>
         <v>20535.899999999998</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition ref="G2:G25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+    <sortCondition ref="G2:G26"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2014,20 +2056,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867434CE-2F54-4206-8AAB-2864B8ABE9CF}">
-  <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="4"/>
-    <col min="4" max="4" width="10.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="11"/>
-    <col min="10" max="10" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.8984375" style="4"/>
+    <col min="4" max="4" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.8984375" style="11"/>
+    <col min="10" max="10" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2062,7 +2104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2099,7 +2141,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2134,7 +2176,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2169,7 +2211,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2204,7 +2246,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -2241,7 +2283,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2276,7 +2318,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -2289,7 +2331,7 @@
       <c r="D8" s="2">
         <v>2424</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="8">
         <v>2181.6</v>
       </c>
       <c r="F8" s="1">
@@ -2311,480 +2353,483 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3">
-        <v>0.17549999999999999</v>
+        <v>7.4800000000000005E-2</v>
       </c>
       <c r="C9" s="4">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="D9" s="2">
-        <v>8775</v>
-      </c>
-      <c r="E9" s="2">
-        <v>7897.5</v>
+        <f>B9*C9</f>
+        <v>1496</v>
+      </c>
+      <c r="E9" s="8">
+        <f>D9</f>
+        <v>1496</v>
       </c>
       <c r="F9" s="1">
         <v>46086</v>
       </c>
       <c r="G9" s="1">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="H9" s="2">
-        <v>435000</v>
+        <v>246000</v>
       </c>
       <c r="I9" s="11">
-        <v>1.82</v>
+        <v>0.89</v>
       </c>
       <c r="J9" s="2">
-        <v>28650</v>
-      </c>
-      <c r="K9">
-        <v>6.59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>13548</v>
+      </c>
+      <c r="K9" s="3">
+        <f>B8+B9</f>
+        <v>0.19600000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3">
-        <v>1.4</v>
+        <v>0.17549999999999999</v>
       </c>
       <c r="C10" s="4">
-        <v>7500</v>
+        <v>50000</v>
       </c>
       <c r="D10" s="2">
-        <v>10500</v>
+        <v>8775</v>
       </c>
       <c r="E10" s="2">
-        <v>9450</v>
+        <v>7897.5</v>
       </c>
       <c r="F10" s="1">
         <v>46086</v>
       </c>
       <c r="G10" s="1">
+        <v>46108</v>
+      </c>
+      <c r="H10" s="2">
+        <v>435000</v>
+      </c>
+      <c r="I10" s="11">
+        <v>1.82</v>
+      </c>
+      <c r="J10" s="2">
+        <v>28650</v>
+      </c>
+      <c r="K10">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="C11" s="4">
+        <v>7500</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10500</v>
+      </c>
+      <c r="E11" s="2">
+        <v>9450</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G11" s="1">
         <v>46140</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H11" s="2">
         <v>240000</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I11" s="11">
         <v>3.94</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J11" s="2">
         <v>17250</v>
       </c>
-      <c r="K10">
+      <c r="K11">
         <v>7.19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B12" s="3">
         <v>0.35</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C12" s="4">
         <v>3600</v>
       </c>
-      <c r="D11" s="2">
-        <f>B11*C11</f>
+      <c r="D12" s="2">
+        <f>B12*C12</f>
         <v>1260</v>
       </c>
-      <c r="E11" s="2">
-        <f>D11*0.9</f>
+      <c r="E12" s="2">
+        <f>D12*0.9</f>
         <v>1134</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F12" s="1">
         <v>46091</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" s="1">
         <v>46157</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H12" s="2">
         <v>41040</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I12" s="11">
         <v>1.97</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J12" s="2">
         <v>1260</v>
       </c>
-      <c r="K11">
+      <c r="K12">
         <v>3.07</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B13" s="3">
         <v>0.27939999999999998</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C13" s="4">
         <v>55000</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D13" s="2">
         <v>15367</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E13" s="2">
         <v>13830.3</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46092</v>
-      </c>
-      <c r="G12" s="1">
-        <v>46108</v>
-      </c>
-      <c r="H12" s="2">
-        <v>990000</v>
-      </c>
-      <c r="I12" s="11">
-        <v>1.4</v>
-      </c>
-      <c r="J12" s="2">
-        <v>45380.5</v>
-      </c>
-      <c r="K12">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="C13" s="4">
-        <v>27000</v>
-      </c>
-      <c r="D13" s="2">
-        <v>40500</v>
-      </c>
-      <c r="E13" s="2">
-        <v>36450</v>
       </c>
       <c r="F13" s="1">
         <v>46092</v>
       </c>
       <c r="G13" s="1">
+        <v>46108</v>
+      </c>
+      <c r="H13" s="2">
+        <v>990000</v>
+      </c>
+      <c r="I13" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="J13" s="2">
+        <v>45380.5</v>
+      </c>
+      <c r="K13">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="C14" s="4">
+        <v>27000</v>
+      </c>
+      <c r="D14" s="2">
+        <v>40500</v>
+      </c>
+      <c r="E14" s="2">
+        <v>36450</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46092</v>
+      </c>
+      <c r="G14" s="1">
         <v>46157</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H14" s="2">
         <v>1047060</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I14" s="11">
         <v>3.48</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J14" s="2">
         <v>67500</v>
       </c>
-      <c r="K13">
+      <c r="K14">
         <v>6.45</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B15" s="3">
         <v>0.48</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C15" s="4">
         <v>1200</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D15" s="2">
         <v>576</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E15" s="2">
         <v>518.4</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F15" s="1">
         <v>46093</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15" s="1">
         <v>46164</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H15" s="2">
         <v>44400</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I15" s="11">
         <v>1.17</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J15" s="2">
         <v>948</v>
       </c>
-      <c r="K14">
+      <c r="K15">
         <v>2.14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B16" s="3">
         <v>1.17</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C16" s="4">
         <v>4000</v>
       </c>
-      <c r="D15" s="2">
-        <f>B15*C15</f>
+      <c r="D16" s="2">
+        <f>B16*C16</f>
         <v>4680</v>
       </c>
-      <c r="E15" s="2">
-        <f>D15*0.9</f>
+      <c r="E16" s="2">
+        <f>D16*0.9</f>
         <v>4212</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F16" s="1">
         <v>46094</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G16" s="1">
         <v>46157</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H16" s="2">
         <v>99600</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I16" s="11">
         <v>3.36</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J16" s="2">
         <v>6920</v>
       </c>
-      <c r="K15">
+      <c r="K16">
         <v>6.95</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B17" s="3">
         <v>0.7</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C17" s="4">
         <v>75000</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D17" s="2">
         <v>52500</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E17" s="2">
         <v>47250</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F17" s="1">
         <v>46132</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G17" s="1">
         <v>46149</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H17" s="2">
         <v>1148400</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I17" s="11">
         <v>4.1100000000000003</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J17" s="2">
         <v>71250</v>
       </c>
-      <c r="K16">
+      <c r="K17">
         <v>6.2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B18" s="3">
         <v>0.5</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C18" s="4">
         <v>10000</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D18" s="2">
         <v>5000</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E18" s="2">
         <v>4500</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F18" s="1">
         <v>46133</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G18" s="1">
         <v>46150</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H18" s="2">
         <v>300000</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I18" s="11">
         <v>1.5</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J18" s="2">
         <v>5000</v>
       </c>
-      <c r="K17">
+      <c r="K18">
         <v>1.67</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B19" s="3">
         <v>0.26</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C19" s="4">
         <v>27000</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D19" s="2">
         <v>7020</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E19" s="2">
         <v>6318</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F19" s="1">
         <v>46135</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G19" s="1">
         <v>46149</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H19" s="2">
         <v>201150</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I19" s="11">
         <v>3.14</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J19" s="2">
         <v>8370</v>
       </c>
-      <c r="K18">
+      <c r="K19">
         <v>4.16</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B20" s="3">
         <v>0.3</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C20" s="4">
         <v>4000</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D20" s="2">
         <v>1200</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E20" s="2">
         <v>1080</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F20" s="1">
         <v>46141</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G20" s="1">
         <v>46164</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H20" s="2">
         <v>86800</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I20" s="11">
         <v>1.24</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J20" s="2">
         <v>1800</v>
       </c>
-      <c r="K19">
+      <c r="K20">
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B21" s="3">
         <v>0.38</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C21" s="4">
         <v>17500</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D21" s="2">
         <v>6650</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E21" s="2">
         <v>5985</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F21" s="1">
         <v>46142</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G21" s="1">
         <v>46154</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H21" s="2">
         <v>462000</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I21" s="11">
         <v>1.3</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J21" s="2">
         <v>8400</v>
       </c>
-      <c r="K20">
+      <c r="K21">
         <v>1.82</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B22" s="3">
         <v>0.25</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C22" s="4">
         <v>10000</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D22" s="2">
         <v>2500</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E22" s="2">
         <v>2250</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46147</v>
-      </c>
-      <c r="G21" s="1">
-        <v>46164</v>
-      </c>
-      <c r="H21" s="2">
-        <v>234000</v>
-      </c>
-      <c r="I21" s="11">
-        <v>0.96</v>
-      </c>
-      <c r="J21" s="2">
-        <v>12500</v>
-      </c>
-      <c r="K21">
-        <v>5.34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="C22" s="4">
-        <v>7200</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1260</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1134</v>
       </c>
       <c r="F22" s="1">
         <v>46147</v>
@@ -2793,215 +2838,250 @@
         <v>46164</v>
       </c>
       <c r="H22" s="2">
+        <v>234000</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="J22" s="2">
+        <v>12500</v>
+      </c>
+      <c r="K22">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C23" s="4">
+        <v>7200</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1260</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1134</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G23" s="1">
+        <v>46164</v>
+      </c>
+      <c r="H23" s="2">
         <v>288000</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I23" s="11">
         <v>0.39</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J23" s="2">
         <v>5040</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>1.75</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B24" s="3">
         <v>0.39</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C24" s="4">
         <v>1000</v>
       </c>
-      <c r="D23" s="2">
-        <f>B23*C23</f>
+      <c r="D24" s="2">
+        <f>B24*C24</f>
         <v>390</v>
       </c>
-      <c r="E23" s="2">
-        <f>D23*0.9</f>
+      <c r="E24" s="2">
+        <f>D24*0.9</f>
         <v>351</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F24" s="1">
         <v>46148</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G24" s="1">
         <v>46168</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H24" s="2">
         <v>26000</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I24" s="11">
         <v>0.93</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J24" s="2">
         <v>630</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>2.42</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B25" s="3">
         <v>0.08</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C25" s="4">
         <v>9000</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D25" s="2">
         <v>720</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E25" s="2">
         <v>648</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F25" s="1">
         <v>46149</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G25" s="1">
         <v>46170</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H25" s="2">
         <v>44640</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I25" s="11">
         <v>1.45</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J25" s="2">
         <v>720</v>
       </c>
-      <c r="K24">
+      <c r="K25">
         <v>1.61</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B26" s="3">
         <v>0.138295</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C26" s="4">
         <v>105000</v>
       </c>
-      <c r="D25" s="2">
-        <f>B25*C25</f>
+      <c r="D26" s="2">
+        <f>B26*C26</f>
         <v>14520.975</v>
       </c>
-      <c r="E25" s="2">
-        <f>D25*0.9</f>
+      <c r="E26" s="2">
+        <f>D26*0.9</f>
         <v>13068.877500000001</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F26" s="1">
         <v>46155</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G26" s="1">
         <v>46167</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H26" s="2">
         <v>470400</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I26" s="11">
         <v>2.78</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J26" s="2">
         <v>14521.5</v>
       </c>
-      <c r="K25">
+      <c r="K26">
         <v>3.09</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E26" s="2">
-        <f>SUM(E2:E25)</f>
-        <v>210138.69150000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E27" s="2">
+        <f>SUM(E2:E26)</f>
+        <v>211634.69150000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B28" s="3">
         <v>0.22412299999999999</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C28" s="4">
         <v>30000</v>
       </c>
-      <c r="D27" s="2">
-        <f>B27*C27</f>
+      <c r="D28" s="2">
+        <f>B28*C28</f>
         <v>6723.69</v>
       </c>
-      <c r="E27" s="2">
-        <f>D27*0.9</f>
+      <c r="E28" s="2">
+        <f>D28*0.9</f>
         <v>6051.3209999999999</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F28" s="1">
         <v>46066</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G28" s="1">
         <v>46085</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H28" s="2">
         <v>1212000</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I28" s="11">
         <v>2</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J28" s="2">
         <v>61908</v>
       </c>
-      <c r="K27">
+      <c r="K28">
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E28" s="2">
-        <f>E2+E27</f>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E29" s="2">
+        <f>E2+E28</f>
         <v>30256.605</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>0.27939999999999998</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C30" s="4">
         <v>24000</v>
       </c>
-      <c r="D29" s="2">
-        <f>B29*C29</f>
+      <c r="D30" s="2">
+        <f>B30*C30</f>
         <v>6705.5999999999995</v>
       </c>
-      <c r="E29" s="2">
-        <f>D29</f>
+      <c r="E30" s="2">
+        <f>D30</f>
         <v>6705.5999999999995</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F30" s="1">
         <v>46092</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G30" s="1">
         <v>46108</v>
       </c>
-      <c r="H29">
+      <c r="H30">
         <v>1</v>
       </c>
-      <c r="I29"/>
-      <c r="J29"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E30" s="2">
-        <f>E11+E29</f>
+      <c r="I30"/>
+      <c r="J30"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E31" s="2">
+        <f>E12+E30</f>
         <v>7839.5999999999995</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition ref="F2:F25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+    <sortCondition ref="F2:F26"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/23-div-25q4.xlsx
+++ b/Excel/23-div-25q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0063A55C-30B0-426C-B81F-226F37731705}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB1BF66E-24DC-4AE2-9366-511FC4EADBE2}"/>
   <bookViews>
-    <workbookView xWindow="4584" yWindow="1284" windowWidth="17808" windowHeight="10152" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
+    <workbookView xWindow="6144" yWindow="864" windowWidth="16332" windowHeight="11364" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
   </bookViews>
   <sheets>
     <sheet name="by paiddate" sheetId="1" r:id="rId1"/>
@@ -696,6 +696,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1015,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCE875A-6415-4391-A62A-3B21647FF184}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
@@ -1297,7 +1301,7 @@
       <c r="D8" s="2">
         <v>15367</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="8">
         <v>13830.3</v>
       </c>
       <c r="F8" s="1">
@@ -2025,8 +2029,8 @@
         <v>6705.5999999999995</v>
       </c>
       <c r="E30" s="2">
-        <f>D30</f>
-        <v>6705.5999999999995</v>
+        <f>D30*0.9</f>
+        <v>6035.04</v>
       </c>
       <c r="F30" s="1">
         <v>46092</v>
@@ -2043,8 +2047,13 @@
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E31" s="2">
         <f>E8+E30</f>
-        <v>20535.899999999998</v>
-      </c>
+        <v>19865.34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">

--- a/Excel/23-div-25q4.xlsx
+++ b/Excel/23-div-25q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB1BF66E-24DC-4AE2-9366-511FC4EADBE2}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86505C86-E121-4DEC-8B6B-4A8EA9FBFF94}"/>
   <bookViews>
     <workbookView xWindow="6144" yWindow="864" windowWidth="16332" windowHeight="11364" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
   </bookViews>
@@ -1283,10 +1283,7 @@
       <c r="K7">
         <v>5.51</v>
       </c>
-      <c r="L7" s="2">
-        <f>SUM(E2:E7)</f>
-        <v>50148.613999999994</v>
-      </c>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1336,7 +1333,7 @@
       <c r="D9" s="2">
         <v>8775</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="8">
         <v>7897.5</v>
       </c>
       <c r="F9" s="1">
@@ -1356,6 +1353,10 @@
       </c>
       <c r="K9">
         <v>6.59</v>
+      </c>
+      <c r="L9" s="2">
+        <f>SUM(E2:E9)</f>
+        <v>71876.41399999999</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1967,8 +1968,8 @@
         <v>211634.69149999999</v>
       </c>
       <c r="L27" s="2">
-        <f>E27-L7</f>
-        <v>161486.07749999998</v>
+        <f>E27-L9</f>
+        <v>139758.2775</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">

--- a/Excel/23-div-25q4.xlsx
+++ b/Excel/23-div-25q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86505C86-E121-4DEC-8B6B-4A8EA9FBFF94}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{293D6AAB-4F75-4AD0-86FA-E7316763C67D}"/>
   <bookViews>
-    <workbookView xWindow="6144" yWindow="864" windowWidth="16332" windowHeight="11364" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="15552" windowHeight="11364" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
   </bookViews>
   <sheets>
     <sheet name="by paiddate" sheetId="1" r:id="rId1"/>
@@ -2057,7 +2057,7 @@
       <c r="J32"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L26">
     <sortCondition ref="G2:G26"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/23-div-25q4.xlsx
+++ b/Excel/23-div-25q4.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{293D6AAB-4F75-4AD0-86FA-E7316763C67D}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B858C663-A42B-411A-B137-30F785D6FDB8}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="15552" windowHeight="11364" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
+    <workbookView xWindow="1296" yWindow="624" windowWidth="15564" windowHeight="11364" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
   </bookViews>
   <sheets>
     <sheet name="by paiddate" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
   <si>
     <t>name</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>WHART</t>
+  </si>
+  <si>
+    <t>ORI</t>
   </si>
 </sst>
 </file>
@@ -1019,14 +1022,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCE875A-6415-4391-A62A-3B21647FF184}">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.8984375" style="4"/>
     <col min="4" max="4" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.8984375" style="11"/>
     <col min="10" max="10" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
@@ -1107,144 +1110,146 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>0.22220000000000001</v>
+        <v>0.22412299999999999</v>
       </c>
       <c r="C3" s="4">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="D3" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E3" s="8">
-        <v>8999.1</v>
+        <f>B3*C3</f>
+        <v>6723.69</v>
+      </c>
+      <c r="E3" s="2">
+        <f>D3*0.9</f>
+        <v>6051.3209999999999</v>
       </c>
       <c r="F3" s="1">
         <v>46066</v>
       </c>
       <c r="G3" s="1">
-        <v>46090</v>
+        <v>46085</v>
       </c>
       <c r="H3" s="2">
-        <v>571500</v>
+        <v>1212000</v>
       </c>
       <c r="I3" s="11">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2">
-        <v>39996</v>
+        <v>61908</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>5.1100000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3">
-        <v>0.17829999999999999</v>
+        <v>0.22220000000000001</v>
       </c>
       <c r="C4" s="4">
-        <v>69000</v>
+        <v>45000</v>
       </c>
       <c r="D4" s="2">
-        <v>12302.7</v>
+        <v>9999</v>
       </c>
       <c r="E4" s="8">
-        <v>11072.43</v>
+        <v>8999.1</v>
       </c>
       <c r="F4" s="1">
-        <v>46079</v>
+        <v>46066</v>
       </c>
       <c r="G4" s="1">
-        <v>46093</v>
+        <v>46090</v>
       </c>
       <c r="H4" s="2">
-        <v>534750</v>
+        <v>571500</v>
       </c>
       <c r="I4" s="11">
-        <v>2.0699999999999998</v>
+        <v>1.57</v>
       </c>
       <c r="J4" s="2">
-        <v>53695.8</v>
+        <v>39996</v>
       </c>
       <c r="K4">
-        <v>10.039999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3">
-        <v>0.12189999999999999</v>
+        <v>0.17829999999999999</v>
       </c>
       <c r="C5" s="4">
-        <v>20000</v>
+        <v>69000</v>
       </c>
       <c r="D5" s="2">
-        <f>B5*C5</f>
-        <v>2438</v>
+        <v>12302.7</v>
       </c>
       <c r="E5" s="8">
-        <f>D5*0.9</f>
-        <v>2194.2000000000003</v>
+        <v>11072.43</v>
       </c>
       <c r="F5" s="1">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="G5" s="1">
-        <v>46099</v>
+        <v>46093</v>
       </c>
       <c r="H5" s="2">
-        <v>144000</v>
+        <v>534750</v>
       </c>
       <c r="I5" s="11">
-        <v>1.42</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="J5" s="2">
-        <v>9326</v>
+        <v>53695.8</v>
       </c>
       <c r="K5">
-        <v>6.48</v>
+        <v>10.039999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3">
-        <v>0.1212</v>
+        <v>0.12189999999999999</v>
       </c>
       <c r="C6" s="4">
         <v>20000</v>
       </c>
       <c r="D6" s="2">
-        <v>2424</v>
+        <f>B6*C6</f>
+        <v>2438</v>
       </c>
       <c r="E6" s="8">
-        <v>2181.6</v>
+        <f>D6*0.9</f>
+        <v>2194.2000000000003</v>
       </c>
       <c r="F6" s="1">
-        <v>46086</v>
+        <v>46080</v>
       </c>
       <c r="G6" s="1">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="H6" s="2">
-        <v>246000</v>
+        <v>144000</v>
       </c>
       <c r="I6" s="11">
-        <v>0.89</v>
+        <v>1.42</v>
       </c>
       <c r="J6" s="2">
-        <v>13548</v>
+        <v>9326</v>
       </c>
       <c r="K6">
-        <v>5.51</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1252,18 +1257,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="3">
-        <v>7.4800000000000005E-2</v>
+        <v>0.1212</v>
       </c>
       <c r="C7" s="4">
         <v>20000</v>
       </c>
       <c r="D7" s="2">
-        <f>B7*C7</f>
-        <v>1496</v>
+        <v>2424</v>
       </c>
       <c r="E7" s="8">
-        <f>D7</f>
-        <v>1496</v>
+        <v>2181.6</v>
       </c>
       <c r="F7" s="1">
         <v>46086</v>
@@ -1283,397 +1286,393 @@
       <c r="K7">
         <v>5.51</v>
       </c>
-      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3">
-        <v>0.27939999999999998</v>
+        <v>7.4800000000000005E-2</v>
       </c>
       <c r="C8" s="4">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="D8" s="2">
-        <v>15367</v>
+        <f>B8*C8</f>
+        <v>1496</v>
       </c>
       <c r="E8" s="8">
-        <v>13830.3</v>
+        <f>D8</f>
+        <v>1496</v>
       </c>
       <c r="F8" s="1">
-        <v>46092</v>
+        <v>46086</v>
       </c>
       <c r="G8" s="1">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="H8" s="2">
-        <v>990000</v>
+        <v>246000</v>
       </c>
       <c r="I8" s="11">
-        <v>1.4</v>
+        <v>0.89</v>
       </c>
       <c r="J8" s="2">
-        <v>45380.5</v>
+        <v>13548</v>
       </c>
       <c r="K8">
-        <v>4.58</v>
-      </c>
+        <v>5.51</v>
+      </c>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3">
-        <v>0.17549999999999999</v>
+        <v>0.27939999999999998</v>
       </c>
       <c r="C9" s="4">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="D9" s="2">
-        <v>8775</v>
+        <v>15367</v>
       </c>
       <c r="E9" s="8">
-        <v>7897.5</v>
+        <v>13830.3</v>
       </c>
       <c r="F9" s="1">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="G9" s="1">
         <v>46108</v>
       </c>
       <c r="H9" s="2">
-        <v>435000</v>
+        <v>990000</v>
       </c>
       <c r="I9" s="11">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="J9" s="2">
-        <v>28650</v>
+        <v>45380.5</v>
       </c>
       <c r="K9">
-        <v>6.59</v>
-      </c>
-      <c r="L9" s="2">
-        <f>SUM(E2:E9)</f>
-        <v>71876.41399999999</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3">
-        <v>0.5</v>
+        <v>0.27939999999999998</v>
       </c>
       <c r="C10" s="4">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="D10" s="2">
-        <v>3000</v>
+        <f>B10*C10</f>
+        <v>6705.5999999999995</v>
       </c>
       <c r="E10" s="2">
-        <v>2700</v>
+        <f>D10*0.9</f>
+        <v>6035.04</v>
       </c>
       <c r="F10" s="1">
-        <v>46077</v>
+        <v>46092</v>
       </c>
       <c r="G10" s="1">
-        <v>46136</v>
-      </c>
-      <c r="H10" s="2">
-        <v>388500</v>
-      </c>
-      <c r="I10" s="11">
-        <v>0.69</v>
-      </c>
-      <c r="J10" s="2">
-        <v>3000</v>
-      </c>
-      <c r="K10">
-        <v>0.77</v>
-      </c>
+        <v>46108</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3">
-        <v>1.4</v>
+        <v>0.17549999999999999</v>
       </c>
       <c r="C11" s="4">
-        <v>7500</v>
+        <v>50000</v>
       </c>
       <c r="D11" s="2">
-        <v>10500</v>
-      </c>
-      <c r="E11" s="2">
-        <v>9450</v>
+        <v>8775</v>
+      </c>
+      <c r="E11" s="8">
+        <v>7897.5</v>
       </c>
       <c r="F11" s="1">
         <v>46086</v>
       </c>
       <c r="G11" s="1">
-        <v>46140</v>
+        <v>46108</v>
       </c>
       <c r="H11" s="2">
-        <v>240000</v>
+        <v>435000</v>
       </c>
       <c r="I11" s="11">
-        <v>3.94</v>
+        <v>1.82</v>
       </c>
       <c r="J11" s="2">
-        <v>17250</v>
+        <v>28650</v>
       </c>
       <c r="K11">
-        <v>7.19</v>
-      </c>
+        <v>6.59</v>
+      </c>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B12" s="3">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="C12" s="4">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="D12" s="2">
-        <v>3010</v>
-      </c>
-      <c r="E12" s="2">
-        <v>2709</v>
+        <v>3000</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2700</v>
       </c>
       <c r="F12" s="1">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G12" s="1">
-        <v>46148</v>
+        <v>46136</v>
       </c>
       <c r="H12" s="2">
-        <v>263900</v>
+        <v>388500</v>
       </c>
       <c r="I12" s="11">
-        <v>1.03</v>
+        <v>0.69</v>
       </c>
       <c r="J12" s="2">
-        <v>4690</v>
+        <v>3000</v>
       </c>
       <c r="K12">
-        <v>1.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="C13" s="4">
-        <v>75000</v>
+        <v>7500</v>
       </c>
       <c r="D13" s="2">
-        <v>52500</v>
-      </c>
-      <c r="E13" s="2">
-        <v>47250</v>
+        <v>10500</v>
+      </c>
+      <c r="E13" s="8">
+        <v>9472.5</v>
       </c>
       <c r="F13" s="1">
-        <v>46132</v>
+        <v>46086</v>
       </c>
       <c r="G13" s="1">
-        <v>46149</v>
+        <v>46140</v>
       </c>
       <c r="H13" s="2">
-        <v>1148400</v>
+        <v>240000</v>
       </c>
       <c r="I13" s="11">
-        <v>4.1100000000000003</v>
+        <v>3.94</v>
       </c>
       <c r="J13" s="2">
-        <v>71250</v>
+        <v>17250</v>
       </c>
       <c r="K13">
-        <v>6.2</v>
+        <v>7.19</v>
+      </c>
+      <c r="L13" s="2">
+        <f>SUM(E4:E13)</f>
+        <v>65878.67</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" s="3">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="C14" s="4">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="D14" s="2">
-        <v>7020</v>
-      </c>
-      <c r="E14" s="2">
-        <v>6318</v>
+        <v>3010</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2709</v>
       </c>
       <c r="F14" s="1">
-        <v>46135</v>
+        <v>46083</v>
       </c>
       <c r="G14" s="1">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="H14" s="2">
-        <v>201150</v>
+        <v>263900</v>
       </c>
       <c r="I14" s="11">
-        <v>3.14</v>
+        <v>1.03</v>
       </c>
       <c r="J14" s="2">
-        <v>8370</v>
+        <v>4690</v>
       </c>
       <c r="K14">
-        <v>4.16</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C15" s="4">
-        <v>10000</v>
+        <v>75000</v>
       </c>
       <c r="D15" s="2">
-        <v>5000</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4500</v>
+        <v>52500</v>
+      </c>
+      <c r="E15" s="8">
+        <v>51975</v>
       </c>
       <c r="F15" s="1">
-        <v>46133</v>
+        <v>46132</v>
       </c>
       <c r="G15" s="1">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="H15" s="2">
-        <v>300000</v>
+        <v>1148400</v>
       </c>
       <c r="I15" s="11">
-        <v>1.5</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="J15" s="2">
-        <v>5000</v>
+        <v>71250</v>
       </c>
       <c r="K15">
-        <v>1.67</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B16" s="3">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="C16" s="4">
-        <v>17500</v>
+        <v>27000</v>
       </c>
       <c r="D16" s="2">
-        <v>6650</v>
-      </c>
-      <c r="E16" s="2">
-        <v>5985</v>
+        <v>7020</v>
+      </c>
+      <c r="E16" s="8">
+        <v>7020</v>
       </c>
       <c r="F16" s="1">
-        <v>46142</v>
+        <v>46135</v>
       </c>
       <c r="G16" s="1">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="H16" s="2">
-        <v>462000</v>
+        <v>201150</v>
       </c>
       <c r="I16" s="11">
-        <v>1.3</v>
+        <v>3.14</v>
       </c>
       <c r="J16" s="2">
-        <v>8400</v>
+        <v>8370</v>
       </c>
       <c r="K16">
-        <v>1.82</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="C17" s="4">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="D17" s="2">
-        <f>B17*C17</f>
-        <v>4680</v>
-      </c>
-      <c r="E17" s="2">
-        <f>D17*0.9</f>
-        <v>4212</v>
+        <v>5000</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4500</v>
       </c>
       <c r="F17" s="1">
-        <v>46094</v>
+        <v>46133</v>
       </c>
       <c r="G17" s="1">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="H17" s="2">
-        <v>99600</v>
+        <v>300000</v>
       </c>
       <c r="I17" s="11">
-        <v>3.36</v>
+        <v>1.5</v>
       </c>
       <c r="J17" s="2">
-        <v>6920</v>
+        <v>5000</v>
       </c>
       <c r="K17">
-        <v>6.95</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B18" s="3">
-        <v>1.5</v>
+        <v>0.38</v>
       </c>
       <c r="C18" s="4">
-        <v>27000</v>
+        <v>17500</v>
       </c>
       <c r="D18" s="2">
-        <v>40500</v>
-      </c>
-      <c r="E18" s="2">
-        <v>36450</v>
+        <v>6650</v>
+      </c>
+      <c r="E18" s="8">
+        <v>5985</v>
       </c>
       <c r="F18" s="1">
-        <v>46092</v>
+        <v>46142</v>
       </c>
       <c r="G18" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="H18" s="2">
-        <v>1047060</v>
+        <v>462000</v>
       </c>
       <c r="I18" s="11">
-        <v>3.48</v>
+        <v>1.3</v>
       </c>
       <c r="J18" s="2">
-        <v>67500</v>
+        <v>8400</v>
       </c>
       <c r="K18">
-        <v>6.45</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1690,14 +1689,14 @@
         <f>B19*C19</f>
         <v>1260</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="8">
         <f>D19*0.9</f>
         <v>1134</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="9">
         <v>45726</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="9">
         <v>46157</v>
       </c>
       <c r="H19" s="2">
@@ -1715,350 +1714,380 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B20" s="3">
-        <v>0.48</v>
+        <v>1.5</v>
       </c>
       <c r="C20" s="4">
-        <v>1200</v>
+        <v>27000</v>
       </c>
       <c r="D20" s="2">
-        <v>576</v>
-      </c>
-      <c r="E20" s="2">
-        <v>518.4</v>
-      </c>
-      <c r="F20" s="1">
-        <v>46093</v>
-      </c>
-      <c r="G20" s="1">
-        <v>46164</v>
+        <v>40500</v>
+      </c>
+      <c r="E20" s="8">
+        <v>38340</v>
+      </c>
+      <c r="F20" s="9">
+        <v>46092</v>
+      </c>
+      <c r="G20" s="9">
+        <v>46157</v>
       </c>
       <c r="H20" s="2">
-        <v>44400</v>
+        <v>1047060</v>
       </c>
       <c r="I20" s="11">
-        <v>1.17</v>
+        <v>3.48</v>
       </c>
       <c r="J20" s="2">
-        <v>948</v>
+        <v>67500</v>
       </c>
       <c r="K20">
-        <v>2.14</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3">
-        <v>0.3</v>
+        <v>1.17</v>
       </c>
       <c r="C21" s="4">
         <v>4000</v>
       </c>
       <c r="D21" s="2">
-        <v>1200</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1080</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46141</v>
-      </c>
-      <c r="G21" s="1">
-        <v>46164</v>
+        <f>B21*C21</f>
+        <v>4680</v>
+      </c>
+      <c r="E21" s="8">
+        <v>4272</v>
+      </c>
+      <c r="F21" s="9">
+        <v>46094</v>
+      </c>
+      <c r="G21" s="9">
+        <v>46157</v>
       </c>
       <c r="H21" s="2">
-        <v>86800</v>
+        <v>99600</v>
       </c>
       <c r="I21" s="11">
-        <v>1.24</v>
+        <v>3.36</v>
       </c>
       <c r="J21" s="2">
-        <v>1800</v>
+        <v>6920</v>
       </c>
       <c r="K21">
-        <v>2.0699999999999998</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B22" s="3">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
       <c r="C22" s="4">
-        <v>10000</v>
+        <v>1200</v>
       </c>
       <c r="D22" s="2">
-        <v>2500</v>
+        <v>576</v>
       </c>
       <c r="E22" s="2">
-        <v>2250</v>
+        <v>518.4</v>
       </c>
       <c r="F22" s="1">
-        <v>46147</v>
+        <v>46093</v>
       </c>
       <c r="G22" s="1">
         <v>46164</v>
       </c>
       <c r="H22" s="2">
-        <v>234000</v>
+        <v>44400</v>
       </c>
       <c r="I22" s="11">
-        <v>0.96</v>
+        <v>1.17</v>
       </c>
       <c r="J22" s="2">
-        <v>12500</v>
+        <v>948</v>
       </c>
       <c r="K22">
-        <v>5.34</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B23" s="3">
-        <v>0.17499999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="C23" s="4">
-        <v>7200</v>
+        <v>4000</v>
       </c>
       <c r="D23" s="2">
-        <v>1260</v>
+        <v>1200</v>
       </c>
       <c r="E23" s="2">
-        <v>1134</v>
+        <v>1080</v>
       </c>
       <c r="F23" s="1">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="G23" s="1">
         <v>46164</v>
       </c>
       <c r="H23" s="2">
-        <v>288000</v>
+        <v>86800</v>
       </c>
       <c r="I23" s="11">
-        <v>0.39</v>
+        <v>1.24</v>
       </c>
       <c r="J23" s="2">
-        <v>5040</v>
+        <v>1800</v>
       </c>
       <c r="K23">
-        <v>1.75</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B24" s="3">
-        <v>0.138295</v>
+        <v>0.25</v>
       </c>
       <c r="C24" s="4">
-        <v>105000</v>
+        <v>10000</v>
       </c>
       <c r="D24" s="2">
-        <f>B24*C24</f>
-        <v>14520.975</v>
+        <v>2500</v>
       </c>
       <c r="E24" s="2">
-        <f>D24*0.9</f>
-        <v>13068.877500000001</v>
+        <v>2250</v>
       </c>
       <c r="F24" s="1">
-        <v>46155</v>
+        <v>46147</v>
       </c>
       <c r="G24" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="H24" s="2">
-        <v>470400</v>
+        <v>234000</v>
       </c>
       <c r="I24" s="11">
-        <v>2.78</v>
+        <v>0.96</v>
       </c>
       <c r="J24" s="2">
-        <v>14521.5</v>
+        <v>12500</v>
       </c>
       <c r="K24">
-        <v>3.09</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B25" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C25" s="4">
+        <v>7200</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1260</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1134</v>
+      </c>
+      <c r="F25" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G25" s="1">
+        <v>46164</v>
+      </c>
+      <c r="H25" s="2">
+        <v>288000</v>
+      </c>
+      <c r="I25" s="11">
         <v>0.39</v>
       </c>
-      <c r="C25" s="4">
-        <v>1000</v>
-      </c>
-      <c r="D25" s="2">
-        <f>B25*C25</f>
-        <v>390</v>
-      </c>
-      <c r="E25" s="2">
-        <f>D25*0.9</f>
-        <v>351</v>
-      </c>
-      <c r="F25" s="1">
-        <v>46148</v>
-      </c>
-      <c r="G25" s="1">
-        <v>46168</v>
-      </c>
-      <c r="H25" s="2">
-        <v>26000</v>
-      </c>
-      <c r="I25" s="11">
-        <v>0.93</v>
-      </c>
       <c r="J25" s="2">
-        <v>630</v>
+        <v>5040</v>
       </c>
       <c r="K25">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B26" s="3">
-        <v>0.08</v>
+        <v>0.138295</v>
       </c>
       <c r="C26" s="4">
-        <v>9000</v>
+        <v>105000</v>
       </c>
       <c r="D26" s="2">
-        <v>720</v>
+        <f>B26*C26</f>
+        <v>14520.975</v>
       </c>
       <c r="E26" s="2">
-        <v>648</v>
+        <f>D26*0.9</f>
+        <v>13068.877500000001</v>
       </c>
       <c r="F26" s="1">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="G26" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="H26" s="2">
-        <v>44640</v>
+        <v>470400</v>
       </c>
       <c r="I26" s="11">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
       <c r="J26" s="2">
-        <v>720</v>
+        <v>14521.5</v>
       </c>
       <c r="K26">
-        <v>1.61</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D27" s="2">
+        <f>B27*C27</f>
+        <v>390</v>
+      </c>
       <c r="E27" s="2">
-        <f>SUM(E2:E26)</f>
-        <v>211634.69149999999</v>
-      </c>
-      <c r="L27" s="2">
-        <f>E27-L9</f>
-        <v>139758.2775</v>
+        <f>D27*0.9</f>
+        <v>351</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46148</v>
+      </c>
+      <c r="G27" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H27" s="2">
+        <v>26000</v>
+      </c>
+      <c r="I27" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="J27" s="2">
+        <v>630</v>
+      </c>
+      <c r="K27">
+        <v>2.42</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B28" s="3">
-        <v>0.22412299999999999</v>
+        <v>0.08</v>
       </c>
       <c r="C28" s="4">
-        <v>30000</v>
+        <v>9000</v>
       </c>
       <c r="D28" s="2">
-        <f>B28*C28</f>
-        <v>6723.69</v>
+        <v>720</v>
       </c>
       <c r="E28" s="2">
-        <f>D28*0.9</f>
-        <v>6051.3209999999999</v>
+        <v>648</v>
       </c>
       <c r="F28" s="1">
-        <v>46066</v>
+        <v>46149</v>
       </c>
       <c r="G28" s="1">
-        <v>46085</v>
+        <v>46170</v>
       </c>
       <c r="H28" s="2">
-        <v>1212000</v>
+        <v>44640</v>
       </c>
       <c r="I28" s="11">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="J28" s="2">
-        <v>61908</v>
+        <v>720</v>
       </c>
       <c r="K28">
-        <v>5.1100000000000003</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="3">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="C29" s="4">
+        <v>50000</v>
+      </c>
+      <c r="D29" s="2">
+        <f>B29*C29</f>
+        <v>2450</v>
+      </c>
       <c r="E29" s="2">
-        <f>E2+E28</f>
-        <v>30256.605</v>
+        <f>D29*0.9</f>
+        <v>2205</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46153</v>
+      </c>
+      <c r="G29" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H29" s="2">
+        <v>44640</v>
+      </c>
+      <c r="I29" s="11">
+        <v>1.45</v>
+      </c>
+      <c r="J29" s="2">
+        <v>720</v>
+      </c>
+      <c r="K29">
+        <v>1.61</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="3">
-        <v>0.27939999999999998</v>
-      </c>
-      <c r="C30" s="4">
-        <v>24000</v>
-      </c>
-      <c r="D30" s="2">
-        <f>B30*C30</f>
-        <v>6705.5999999999995</v>
-      </c>
       <c r="E30" s="2">
-        <f>D30*0.9</f>
-        <v>6035.04</v>
-      </c>
-      <c r="F30" s="1">
-        <v>46092</v>
-      </c>
-      <c r="G30" s="1">
-        <v>46108</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30"/>
-      <c r="J30"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E31" s="2">
-        <f>E8+E30</f>
-        <v>19865.34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
+        <f>SUM(E2:E29)</f>
+        <v>233325.55249999999</v>
+      </c>
+      <c r="L30" s="2">
+        <f>E30-L13</f>
+        <v>167446.88250000001</v>
+      </c>
+    </row>
+    <row r="33" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L26">
-    <sortCondition ref="G2:G26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L33">
+    <sortCondition ref="G2:G33"/>
+    <sortCondition ref="A2:A33"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2066,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867434CE-2F54-4206-8AAB-2864B8ABE9CF}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
@@ -2199,7 +2228,7 @@
       <c r="D4" s="2">
         <v>3000</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="8">
         <v>2700</v>
       </c>
       <c r="F4" s="1">
@@ -2306,7 +2335,7 @@
       <c r="D7" s="2">
         <v>3010</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="8">
         <v>2709</v>
       </c>
       <c r="F7" s="1">
@@ -2449,8 +2478,8 @@
       <c r="D11" s="2">
         <v>10500</v>
       </c>
-      <c r="E11" s="2">
-        <v>9450</v>
+      <c r="E11" s="8">
+        <v>9472.5</v>
       </c>
       <c r="F11" s="1">
         <v>46086</v>
@@ -2663,8 +2692,8 @@
       <c r="D17" s="2">
         <v>52500</v>
       </c>
-      <c r="E17" s="2">
-        <v>47250</v>
+      <c r="E17" s="8">
+        <v>51975</v>
       </c>
       <c r="F17" s="1">
         <v>46132</v>
@@ -2698,7 +2727,7 @@
       <c r="D18" s="2">
         <v>5000</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="8">
         <v>4500</v>
       </c>
       <c r="F18" s="1">
@@ -2733,8 +2762,8 @@
       <c r="D19" s="2">
         <v>7020</v>
       </c>
-      <c r="E19" s="2">
-        <v>6318</v>
+      <c r="E19" s="8">
+        <v>7020</v>
       </c>
       <c r="F19" s="1">
         <v>46135</v>
@@ -2969,129 +2998,166 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B26" s="3">
-        <v>0.138295</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="C26" s="4">
-        <v>105000</v>
+        <v>50000</v>
       </c>
       <c r="D26" s="2">
         <f>B26*C26</f>
-        <v>14520.975</v>
+        <v>2450</v>
       </c>
       <c r="E26" s="2">
         <f>D26*0.9</f>
+        <v>2205</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46153</v>
+      </c>
+      <c r="G26" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H26" s="2">
+        <v>44640</v>
+      </c>
+      <c r="I26" s="11">
+        <v>1.45</v>
+      </c>
+      <c r="J26" s="2">
+        <v>720</v>
+      </c>
+      <c r="K26">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0.138295</v>
+      </c>
+      <c r="C27" s="4">
+        <v>105000</v>
+      </c>
+      <c r="D27" s="2">
+        <f>B27*C27</f>
+        <v>14520.975</v>
+      </c>
+      <c r="E27" s="2">
+        <f>D27*0.9</f>
         <v>13068.877500000001</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F27" s="1">
         <v>46155</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G27" s="1">
         <v>46167</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H27" s="2">
         <v>470400</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I27" s="11">
         <v>2.78</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J27" s="2">
         <v>14521.5</v>
       </c>
-      <c r="K26">
+      <c r="K27">
         <v>3.09</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E27" s="2">
-        <f>SUM(E2:E26)</f>
-        <v>211634.69150000002</v>
-      </c>
-    </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="E28" s="2">
+        <f>SUM(E2:E27)</f>
+        <v>219289.19150000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <v>0.22412299999999999</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C29" s="4">
         <v>30000</v>
       </c>
-      <c r="D28" s="2">
-        <f>B28*C28</f>
+      <c r="D29" s="2">
+        <f>B29*C29</f>
         <v>6723.69</v>
       </c>
-      <c r="E28" s="2">
-        <f>D28*0.9</f>
+      <c r="E29" s="2">
+        <f>D29*0.9</f>
         <v>6051.3209999999999</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F29" s="1">
         <v>46066</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G29" s="1">
         <v>46085</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H29" s="2">
         <v>1212000</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I29" s="11">
         <v>2</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J29" s="2">
         <v>61908</v>
       </c>
-      <c r="K28">
+      <c r="K29">
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E29" s="2">
-        <f>E2+E28</f>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E30" s="2">
+        <f>E2+E29</f>
         <v>30256.605</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <v>0.27939999999999998</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C31" s="4">
         <v>24000</v>
       </c>
-      <c r="D30" s="2">
-        <f>B30*C30</f>
+      <c r="D31" s="2">
+        <f>B31*C31</f>
         <v>6705.5999999999995</v>
       </c>
-      <c r="E30" s="2">
-        <f>D30</f>
+      <c r="E31" s="2">
+        <f>D31</f>
         <v>6705.5999999999995</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F31" s="1">
         <v>46092</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G31" s="1">
         <v>46108</v>
       </c>
-      <c r="H30">
+      <c r="H31">
         <v>1</v>
       </c>
-      <c r="I30"/>
-      <c r="J30"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E31" s="2">
-        <f>E12+E30</f>
+      <c r="I31"/>
+      <c r="J31"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E32" s="2">
+        <f>E12+E31</f>
         <v>7839.5999999999995</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition ref="F2:F26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K27">
+    <sortCondition ref="F2:F27"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/23-div-25q4.xlsx
+++ b/Excel/23-div-25q4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B858C663-A42B-411A-B137-30F785D6FDB8}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7B89608-D0B4-441D-BE54-44D31022057A}"/>
   <bookViews>
-    <workbookView xWindow="1296" yWindow="624" windowWidth="15564" windowHeight="11364" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
+    <workbookView xWindow="2304" yWindow="2196" windowWidth="10044" windowHeight="10764" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
   </bookViews>
   <sheets>
     <sheet name="by paiddate" sheetId="1" r:id="rId1"/>
@@ -149,29 +149,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="187" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="188" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="189" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -179,7 +179,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -187,7 +187,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -195,35 +195,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -231,7 +231,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -239,14 +239,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -254,14 +254,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -269,7 +269,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -277,14 +277,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -632,15 +632,15 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -1023,20 +1023,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCE875A-6415-4391-A62A-3B21647FF184}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.8984375" style="4"/>
-    <col min="4" max="4" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.8984375" style="11"/>
-    <col min="10" max="10" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="4"/>
+    <col min="4" max="4" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="11"/>
+    <col min="10" max="10" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1390,7 +1390,7 @@
       <c r="I10"/>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>65878.67</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1796,8 +1796,8 @@
       <c r="D22" s="2">
         <v>576</v>
       </c>
-      <c r="E22" s="2">
-        <v>518.4</v>
+      <c r="E22" s="8">
+        <v>526.79999999999995</v>
       </c>
       <c r="F22" s="1">
         <v>46093</v>
@@ -1818,7 +1818,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -1831,7 +1831,7 @@
       <c r="D23" s="2">
         <v>1200</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="8">
         <v>1080</v>
       </c>
       <c r="F23" s="1">
@@ -1853,7 +1853,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1866,7 +1866,7 @@
       <c r="D24" s="2">
         <v>2500</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="8">
         <v>2250</v>
       </c>
       <c r="F24" s="1">
@@ -1888,7 +1888,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -1901,7 +1901,7 @@
       <c r="D25" s="2">
         <v>1260</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="8">
         <v>1134</v>
       </c>
       <c r="F25" s="1">
@@ -1923,7 +1923,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1937,7 +1937,7 @@
         <f>B26*C26</f>
         <v>14520.975</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="8">
         <f>D26*0.9</f>
         <v>13068.877500000001</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -2069,17 +2069,17 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E30" s="2">
         <f>SUM(E2:E29)</f>
-        <v>233325.55249999999</v>
+        <v>233333.95249999998</v>
       </c>
       <c r="L30" s="2">
         <f>E30-L13</f>
-        <v>167446.88250000001</v>
-      </c>
-    </row>
-    <row r="33" spans="8:10" x14ac:dyDescent="0.25">
+        <v>167455.28249999997</v>
+      </c>
+    </row>
+    <row r="33" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33"/>
@@ -2096,19 +2096,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867434CE-2F54-4206-8AAB-2864B8ABE9CF}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.8984375" style="4"/>
-    <col min="4" max="4" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.8984375" style="11"/>
-    <col min="10" max="10" width="10.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="4"/>
+    <col min="4" max="4" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="11"/>
+    <col min="10" max="10" width="10.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -3070,13 +3070,13 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E28" s="2">
         <f>SUM(E2:E27)</f>
         <v>219289.19150000002</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3113,13 +3113,13 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E30" s="2">
         <f>E2+E29</f>
         <v>30256.605</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -3149,7 +3149,7 @@
       <c r="I31"/>
       <c r="J31"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E32" s="2">
         <f>E12+E31</f>
         <v>7839.5999999999995</v>

--- a/Excel/23-div-25q4.xlsx
+++ b/Excel/23-div-25q4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7B89608-D0B4-441D-BE54-44D31022057A}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="8_{2E0EA41F-FDE7-4828-8D12-869A955280FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE995D83-90BE-4483-966A-03E2C8557691}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2196" windowWidth="10044" windowHeight="10764" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
+    <workbookView xWindow="11892" yWindow="768" windowWidth="10188" windowHeight="10764" xr2:uid="{BC7C96CF-573F-4E03-9013-5FFA1DAA44FA}"/>
   </bookViews>
   <sheets>
     <sheet name="by paiddate" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
   <si>
     <t>name</t>
   </si>
@@ -1974,7 +1974,7 @@
         <f>B27*C27</f>
         <v>390</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="8">
         <f>D27*0.9</f>
         <v>351</v>
       </c>
@@ -2010,7 +2010,7 @@
       <c r="D28" s="2">
         <v>720</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="8">
         <v>648</v>
       </c>
       <c r="F28" s="1">
@@ -2046,7 +2046,7 @@
         <f>B29*C29</f>
         <v>2450</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="8">
         <f>D29*0.9</f>
         <v>2205</v>
       </c>
@@ -2079,6 +2079,7 @@
         <v>167455.28249999997</v>
       </c>
     </row>
+    <row r="32" spans="1:12" ht="9.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H33"/>
       <c r="I33"/>
@@ -2157,7 +2158,7 @@
         <f>B2*C2</f>
         <v>26894.76</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="8">
         <f>D2*0.9</f>
         <v>24205.284</v>
       </c>
@@ -2182,72 +2183,74 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>0.22220000000000001</v>
+        <v>0.22412299999999999</v>
       </c>
       <c r="C3" s="4">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="D3" s="2">
-        <v>9999</v>
+        <f>B3*C3</f>
+        <v>6723.69</v>
       </c>
       <c r="E3" s="2">
-        <v>8999.1</v>
+        <f>D3*0.9</f>
+        <v>6051.3209999999999</v>
       </c>
       <c r="F3" s="1">
         <v>46066</v>
       </c>
       <c r="G3" s="1">
-        <v>46090</v>
+        <v>46085</v>
       </c>
       <c r="H3" s="2">
-        <v>571500</v>
+        <v>1212000</v>
       </c>
       <c r="I3" s="11">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2">
-        <v>39996</v>
+        <v>61908</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>5.1100000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3">
-        <v>0.5</v>
+        <v>0.22220000000000001</v>
       </c>
       <c r="C4" s="4">
-        <v>6000</v>
+        <v>45000</v>
       </c>
       <c r="D4" s="2">
-        <v>3000</v>
+        <v>9999</v>
       </c>
       <c r="E4" s="8">
-        <v>2700</v>
+        <v>8999.1</v>
       </c>
       <c r="F4" s="1">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G4" s="1">
-        <v>46136</v>
+        <v>46090</v>
       </c>
       <c r="H4" s="2">
-        <v>388500</v>
+        <v>571500</v>
       </c>
       <c r="I4" s="11">
-        <v>0.69</v>
+        <v>1.57</v>
       </c>
       <c r="J4" s="2">
-        <v>3000</v>
+        <v>39996</v>
       </c>
       <c r="K4">
-        <v>0.77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2263,7 +2266,7 @@
       <c r="D5" s="2">
         <v>12302.7</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="8">
         <v>11072.43</v>
       </c>
       <c r="F5" s="1">
@@ -2324,37 +2327,37 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
-        <v>0.43</v>
+        <v>0.1212</v>
       </c>
       <c r="C7" s="4">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="D7" s="2">
-        <v>3010</v>
+        <v>2424</v>
       </c>
       <c r="E7" s="8">
-        <v>2709</v>
+        <v>2181.6</v>
       </c>
       <c r="F7" s="1">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="G7" s="1">
-        <v>46148</v>
+        <v>46101</v>
       </c>
       <c r="H7" s="2">
-        <v>263900</v>
+        <v>246000</v>
       </c>
       <c r="I7" s="11">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="J7" s="2">
-        <v>4690</v>
+        <v>13548</v>
       </c>
       <c r="K7">
-        <v>1.78</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -2362,16 +2365,18 @@
         <v>34</v>
       </c>
       <c r="B8" s="3">
-        <v>0.1212</v>
+        <v>7.4800000000000005E-2</v>
       </c>
       <c r="C8" s="4">
         <v>20000</v>
       </c>
       <c r="D8" s="2">
-        <v>2424</v>
+        <f>B8*C8</f>
+        <v>1496</v>
       </c>
       <c r="E8" s="8">
-        <v>2181.6</v>
+        <f>D8</f>
+        <v>1496</v>
       </c>
       <c r="F8" s="1">
         <v>46086</v>
@@ -2394,729 +2399,747 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3">
-        <v>7.4800000000000005E-2</v>
+        <v>0.27939999999999998</v>
       </c>
       <c r="C9" s="4">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="D9" s="2">
-        <f>B9*C9</f>
-        <v>1496</v>
+        <v>15367</v>
       </c>
       <c r="E9" s="8">
-        <f>D9</f>
-        <v>1496</v>
+        <v>13830.3</v>
       </c>
       <c r="F9" s="1">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="G9" s="1">
-        <v>46101</v>
+        <v>46108</v>
       </c>
       <c r="H9" s="2">
-        <v>246000</v>
+        <v>990000</v>
       </c>
       <c r="I9" s="11">
-        <v>0.89</v>
+        <v>1.4</v>
       </c>
       <c r="J9" s="2">
-        <v>13548</v>
-      </c>
-      <c r="K9" s="3">
-        <f>B8+B9</f>
-        <v>0.19600000000000001</v>
+        <v>45380.5</v>
+      </c>
+      <c r="K9">
+        <v>4.58</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3">
-        <v>0.17549999999999999</v>
+        <v>0.27939999999999998</v>
       </c>
       <c r="C10" s="4">
-        <v>50000</v>
+        <v>24000</v>
       </c>
       <c r="D10" s="2">
-        <v>8775</v>
+        <f>B10*C10</f>
+        <v>6705.5999999999995</v>
       </c>
       <c r="E10" s="2">
-        <v>7897.5</v>
+        <f>D10*0.9</f>
+        <v>6035.04</v>
       </c>
       <c r="F10" s="1">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="G10" s="1">
         <v>46108</v>
       </c>
-      <c r="H10" s="2">
-        <v>435000</v>
-      </c>
-      <c r="I10" s="11">
-        <v>1.82</v>
-      </c>
-      <c r="J10" s="2">
-        <v>28650</v>
-      </c>
-      <c r="K10">
-        <v>6.59</v>
-      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3">
-        <v>1.4</v>
+        <v>0.17549999999999999</v>
       </c>
       <c r="C11" s="4">
-        <v>7500</v>
+        <v>50000</v>
       </c>
       <c r="D11" s="2">
-        <v>10500</v>
+        <v>8775</v>
       </c>
       <c r="E11" s="8">
-        <v>9472.5</v>
+        <v>7897.5</v>
       </c>
       <c r="F11" s="1">
         <v>46086</v>
       </c>
       <c r="G11" s="1">
-        <v>46140</v>
+        <v>46108</v>
       </c>
       <c r="H11" s="2">
-        <v>240000</v>
+        <v>435000</v>
       </c>
       <c r="I11" s="11">
-        <v>3.94</v>
+        <v>1.82</v>
       </c>
       <c r="J11" s="2">
-        <v>17250</v>
+        <v>28650</v>
       </c>
       <c r="K11">
-        <v>7.19</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B12" s="3">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="C12" s="4">
-        <v>3600</v>
+        <v>6000</v>
       </c>
       <c r="D12" s="2">
-        <f>B12*C12</f>
-        <v>1260</v>
-      </c>
-      <c r="E12" s="2">
-        <f>D12*0.9</f>
-        <v>1134</v>
+        <v>3000</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2700</v>
       </c>
       <c r="F12" s="1">
-        <v>46091</v>
+        <v>46077</v>
       </c>
       <c r="G12" s="1">
-        <v>46157</v>
+        <v>46136</v>
       </c>
       <c r="H12" s="2">
-        <v>41040</v>
+        <v>388500</v>
       </c>
       <c r="I12" s="11">
-        <v>1.97</v>
+        <v>0.69</v>
       </c>
       <c r="J12" s="2">
-        <v>1260</v>
+        <v>3000</v>
       </c>
       <c r="K12">
-        <v>3.07</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3">
-        <v>0.27939999999999998</v>
+        <v>1.4</v>
       </c>
       <c r="C13" s="4">
-        <v>55000</v>
+        <v>7500</v>
       </c>
       <c r="D13" s="2">
-        <v>15367</v>
-      </c>
-      <c r="E13" s="2">
-        <v>13830.3</v>
+        <v>10500</v>
+      </c>
+      <c r="E13" s="8">
+        <v>9472.5</v>
       </c>
       <c r="F13" s="1">
-        <v>46092</v>
+        <v>46086</v>
       </c>
       <c r="G13" s="1">
-        <v>46108</v>
+        <v>46140</v>
       </c>
       <c r="H13" s="2">
-        <v>990000</v>
+        <v>240000</v>
       </c>
       <c r="I13" s="11">
-        <v>1.4</v>
+        <v>3.94</v>
       </c>
       <c r="J13" s="2">
-        <v>45380.5</v>
+        <v>17250</v>
       </c>
       <c r="K13">
-        <v>4.58</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B14" s="3">
-        <v>1.5</v>
+        <v>0.43</v>
       </c>
       <c r="C14" s="4">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="D14" s="2">
-        <v>40500</v>
-      </c>
-      <c r="E14" s="2">
-        <v>36450</v>
+        <v>3010</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2709</v>
       </c>
       <c r="F14" s="1">
-        <v>46092</v>
+        <v>46083</v>
       </c>
       <c r="G14" s="1">
-        <v>46157</v>
+        <v>46148</v>
       </c>
       <c r="H14" s="2">
-        <v>1047060</v>
+        <v>263900</v>
       </c>
       <c r="I14" s="11">
-        <v>3.48</v>
+        <v>1.03</v>
       </c>
       <c r="J14" s="2">
-        <v>67500</v>
+        <v>4690</v>
       </c>
       <c r="K14">
-        <v>6.45</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="C15" s="4">
-        <v>1200</v>
+        <v>75000</v>
       </c>
       <c r="D15" s="2">
-        <v>576</v>
-      </c>
-      <c r="E15" s="2">
-        <v>518.4</v>
+        <v>52500</v>
+      </c>
+      <c r="E15" s="8">
+        <v>51975</v>
       </c>
       <c r="F15" s="1">
-        <v>46093</v>
+        <v>46132</v>
       </c>
       <c r="G15" s="1">
-        <v>46164</v>
+        <v>46149</v>
       </c>
       <c r="H15" s="2">
-        <v>44400</v>
+        <v>1148400</v>
       </c>
       <c r="I15" s="11">
-        <v>1.17</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="J15" s="2">
-        <v>948</v>
+        <v>71250</v>
       </c>
       <c r="K15">
-        <v>2.14</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B16" s="3">
-        <v>1.17</v>
+        <v>0.26</v>
       </c>
       <c r="C16" s="4">
-        <v>4000</v>
+        <v>27000</v>
       </c>
       <c r="D16" s="2">
-        <f>B16*C16</f>
-        <v>4680</v>
-      </c>
-      <c r="E16" s="2">
-        <f>D16*0.9</f>
-        <v>4212</v>
+        <v>7020</v>
+      </c>
+      <c r="E16" s="8">
+        <v>7020</v>
       </c>
       <c r="F16" s="1">
-        <v>46094</v>
+        <v>46135</v>
       </c>
       <c r="G16" s="1">
-        <v>46157</v>
+        <v>46149</v>
       </c>
       <c r="H16" s="2">
-        <v>99600</v>
+        <v>201150</v>
       </c>
       <c r="I16" s="11">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="J16" s="2">
-        <v>6920</v>
+        <v>8370</v>
       </c>
       <c r="K16">
-        <v>6.95</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C17" s="4">
-        <v>75000</v>
+        <v>10000</v>
       </c>
       <c r="D17" s="2">
-        <v>52500</v>
+        <v>5000</v>
       </c>
       <c r="E17" s="8">
-        <v>51975</v>
+        <v>4500</v>
       </c>
       <c r="F17" s="1">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="G17" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H17" s="2">
-        <v>1148400</v>
+        <v>300000</v>
       </c>
       <c r="I17" s="11">
-        <v>4.1100000000000003</v>
+        <v>1.5</v>
       </c>
       <c r="J17" s="2">
-        <v>71250</v>
+        <v>5000</v>
       </c>
       <c r="K17">
-        <v>6.2</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="3">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="C18" s="4">
-        <v>10000</v>
+        <v>17500</v>
       </c>
       <c r="D18" s="2">
-        <v>5000</v>
+        <v>6650</v>
       </c>
       <c r="E18" s="8">
-        <v>4500</v>
+        <v>5985</v>
       </c>
       <c r="F18" s="1">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="G18" s="1">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="H18" s="2">
-        <v>300000</v>
+        <v>462000</v>
       </c>
       <c r="I18" s="11">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J18" s="2">
-        <v>5000</v>
+        <v>8400</v>
       </c>
       <c r="K18">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="C19" s="4">
-        <v>27000</v>
+        <v>3600</v>
       </c>
       <c r="D19" s="2">
-        <v>7020</v>
+        <f>B19*C19</f>
+        <v>1260</v>
       </c>
       <c r="E19" s="8">
-        <v>7020</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46135</v>
-      </c>
-      <c r="G19" s="1">
-        <v>46149</v>
+        <f>D19*0.9</f>
+        <v>1134</v>
+      </c>
+      <c r="F19" s="9">
+        <v>45726</v>
+      </c>
+      <c r="G19" s="9">
+        <v>46157</v>
       </c>
       <c r="H19" s="2">
-        <v>201150</v>
+        <v>41040</v>
       </c>
       <c r="I19" s="11">
-        <v>3.14</v>
+        <v>1.97</v>
       </c>
       <c r="J19" s="2">
-        <v>8370</v>
+        <v>1260</v>
       </c>
       <c r="K19">
-        <v>4.16</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B20" s="3">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="C20" s="4">
-        <v>4000</v>
+        <v>27000</v>
       </c>
       <c r="D20" s="2">
-        <v>1200</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1080</v>
-      </c>
-      <c r="F20" s="1">
-        <v>46141</v>
-      </c>
-      <c r="G20" s="1">
-        <v>46164</v>
+        <v>40500</v>
+      </c>
+      <c r="E20" s="8">
+        <v>38340</v>
+      </c>
+      <c r="F20" s="9">
+        <v>46092</v>
+      </c>
+      <c r="G20" s="9">
+        <v>46157</v>
       </c>
       <c r="H20" s="2">
-        <v>86800</v>
+        <v>1047060</v>
       </c>
       <c r="I20" s="11">
-        <v>1.24</v>
+        <v>3.48</v>
       </c>
       <c r="J20" s="2">
-        <v>1800</v>
+        <v>67500</v>
       </c>
       <c r="K20">
-        <v>2.0699999999999998</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3">
-        <v>0.38</v>
+        <v>1.17</v>
       </c>
       <c r="C21" s="4">
-        <v>17500</v>
+        <v>4000</v>
       </c>
       <c r="D21" s="2">
-        <v>6650</v>
-      </c>
-      <c r="E21" s="2">
-        <v>5985</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46142</v>
-      </c>
-      <c r="G21" s="1">
-        <v>46154</v>
+        <f>B21*C21</f>
+        <v>4680</v>
+      </c>
+      <c r="E21" s="8">
+        <v>4272</v>
+      </c>
+      <c r="F21" s="9">
+        <v>46094</v>
+      </c>
+      <c r="G21" s="9">
+        <v>46157</v>
       </c>
       <c r="H21" s="2">
-        <v>462000</v>
+        <v>99600</v>
       </c>
       <c r="I21" s="11">
-        <v>1.3</v>
+        <v>3.36</v>
       </c>
       <c r="J21" s="2">
-        <v>8400</v>
+        <v>6920</v>
       </c>
       <c r="K21">
-        <v>1.82</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B22" s="3">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
       <c r="C22" s="4">
-        <v>10000</v>
+        <v>1200</v>
       </c>
       <c r="D22" s="2">
-        <v>2500</v>
-      </c>
-      <c r="E22" s="2">
-        <v>2250</v>
+        <v>576</v>
+      </c>
+      <c r="E22" s="8">
+        <v>526.79999999999995</v>
       </c>
       <c r="F22" s="1">
-        <v>46147</v>
+        <v>46093</v>
       </c>
       <c r="G22" s="1">
         <v>46164</v>
       </c>
       <c r="H22" s="2">
-        <v>234000</v>
+        <v>44400</v>
       </c>
       <c r="I22" s="11">
-        <v>0.96</v>
+        <v>1.17</v>
       </c>
       <c r="J22" s="2">
-        <v>12500</v>
+        <v>948</v>
       </c>
       <c r="K22">
-        <v>5.34</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B23" s="3">
-        <v>0.17499999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="C23" s="4">
-        <v>7200</v>
+        <v>4000</v>
       </c>
       <c r="D23" s="2">
-        <v>1260</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1134</v>
+        <v>1200</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1080</v>
       </c>
       <c r="F23" s="1">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="G23" s="1">
         <v>46164</v>
       </c>
       <c r="H23" s="2">
-        <v>288000</v>
+        <v>86800</v>
       </c>
       <c r="I23" s="11">
-        <v>0.39</v>
+        <v>1.24</v>
       </c>
       <c r="J23" s="2">
-        <v>5040</v>
+        <v>1800</v>
       </c>
       <c r="K23">
-        <v>1.75</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B24" s="3">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="C24" s="4">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="D24" s="2">
-        <f>B24*C24</f>
-        <v>390</v>
-      </c>
-      <c r="E24" s="2">
-        <f>D24*0.9</f>
-        <v>351</v>
+        <v>2500</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2250</v>
       </c>
       <c r="F24" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="G24" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="H24" s="2">
-        <v>26000</v>
+        <v>234000</v>
       </c>
       <c r="I24" s="11">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="J24" s="2">
-        <v>630</v>
+        <v>12500</v>
       </c>
       <c r="K24">
-        <v>2.42</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>0.08</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="C25" s="4">
-        <v>9000</v>
+        <v>7200</v>
       </c>
       <c r="D25" s="2">
-        <v>720</v>
-      </c>
-      <c r="E25" s="2">
-        <v>648</v>
+        <v>1260</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1134</v>
       </c>
       <c r="F25" s="1">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="G25" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="H25" s="2">
-        <v>44640</v>
+        <v>288000</v>
       </c>
       <c r="I25" s="11">
-        <v>1.45</v>
+        <v>0.39</v>
       </c>
       <c r="J25" s="2">
-        <v>720</v>
+        <v>5040</v>
       </c>
       <c r="K25">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B26" s="3">
-        <v>4.9000000000000002E-2</v>
+        <v>0.138295</v>
       </c>
       <c r="C26" s="4">
-        <v>50000</v>
+        <v>105000</v>
       </c>
       <c r="D26" s="2">
         <f>B26*C26</f>
-        <v>2450</v>
-      </c>
-      <c r="E26" s="2">
+        <v>14520.975</v>
+      </c>
+      <c r="E26" s="8">
         <f>D26*0.9</f>
-        <v>2205</v>
+        <v>13068.877500000001</v>
       </c>
       <c r="F26" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="G26" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="H26" s="2">
-        <v>44640</v>
+        <v>470400</v>
       </c>
       <c r="I26" s="11">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
       <c r="J26" s="2">
-        <v>720</v>
+        <v>14521.5</v>
       </c>
       <c r="K26">
-        <v>1.61</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B27" s="3">
-        <v>0.138295</v>
+        <v>0.39</v>
       </c>
       <c r="C27" s="4">
-        <v>105000</v>
+        <v>1000</v>
       </c>
       <c r="D27" s="2">
         <f>B27*C27</f>
-        <v>14520.975</v>
-      </c>
-      <c r="E27" s="2">
+        <v>390</v>
+      </c>
+      <c r="E27" s="8">
         <f>D27*0.9</f>
-        <v>13068.877500000001</v>
+        <v>351</v>
       </c>
       <c r="F27" s="1">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="G27" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="H27" s="2">
-        <v>470400</v>
+        <v>26000</v>
       </c>
       <c r="I27" s="11">
-        <v>2.78</v>
+        <v>0.93</v>
       </c>
       <c r="J27" s="2">
-        <v>14521.5</v>
+        <v>630</v>
       </c>
       <c r="K27">
-        <v>3.09</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E28" s="2">
-        <f>SUM(E2:E27)</f>
-        <v>219289.19150000002</v>
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="C28" s="4">
+        <v>9000</v>
+      </c>
+      <c r="D28" s="2">
+        <v>720</v>
+      </c>
+      <c r="E28" s="8">
+        <v>648</v>
+      </c>
+      <c r="F28" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G28" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H28" s="2">
+        <v>44640</v>
+      </c>
+      <c r="I28" s="11">
+        <v>1.45</v>
+      </c>
+      <c r="J28" s="2">
+        <v>720</v>
+      </c>
+      <c r="K28">
+        <v>1.61</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B29" s="3">
-        <v>0.22412299999999999</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="C29" s="4">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="D29" s="2">
         <f>B29*C29</f>
-        <v>6723.69</v>
-      </c>
-      <c r="E29" s="2">
+        <v>2450</v>
+      </c>
+      <c r="E29" s="8">
         <f>D29*0.9</f>
-        <v>6051.3209999999999</v>
+        <v>2205</v>
       </c>
       <c r="F29" s="1">
-        <v>46066</v>
+        <v>46153</v>
       </c>
       <c r="G29" s="1">
-        <v>46085</v>
+        <v>46170</v>
       </c>
       <c r="H29" s="2">
-        <v>1212000</v>
+        <v>44640</v>
       </c>
       <c r="I29" s="11">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="J29" s="2">
-        <v>61908</v>
+        <v>720</v>
       </c>
       <c r="K29">
-        <v>5.1100000000000003</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E30" s="2">
-        <f>E2+E29</f>
-        <v>30256.605</v>
+        <f>SUM(E2:E29)</f>
+        <v>233333.95249999998</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -3152,7 +3175,7 @@
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E32" s="2">
         <f>E12+E31</f>
-        <v>7839.5999999999995</v>
+        <v>9405.5999999999985</v>
       </c>
     </row>
   </sheetData>
